--- a/reports/Planning Report.xlsx
+++ b/reports/Planning Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D74D047DAF775038/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZMis_cosas\UNI\DP2_2026\Workspace-26\Projects\Acme-Starters-B\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{615595C2-D3CB-454A-9A2F-7DF7C1749B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D25F628-DEFE-49A4-9EE7-4C8B69EDEC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="148">
   <si>
     <t>Copyright</t>
   </si>
@@ -491,6 +491,18 @@
   </si>
   <si>
     <t>O</t>
+  </si>
+  <si>
+    <t>Create the github fork</t>
+  </si>
+  <si>
+    <t>T0001/M</t>
+  </si>
+  <si>
+    <t>Upload the necesary project changes for the new framework</t>
+  </si>
+  <si>
+    <t>T0003/M</t>
   </si>
 </sst>
 </file>
@@ -500,7 +512,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$EUR]\ #,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1517,12 +1529,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BB59C7-21D2-4063-B60E-B9743CBEBCDD}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1547,7 @@
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="56" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1560,7 @@
       <c r="I4" s="57"/>
       <c r="J4" s="57"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="57"/>
       <c r="C5" s="57"/>
       <c r="D5" s="57"/>
@@ -1559,7 +1571,7 @@
       <c r="I5" s="57"/>
       <c r="J5" s="57"/>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="57"/>
       <c r="C6" s="57"/>
       <c r="D6" s="57"/>
@@ -1570,7 +1582,7 @@
       <c r="I6" s="57"/>
       <c r="J6" s="57"/>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="57"/>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
@@ -1581,7 +1593,7 @@
       <c r="I7" s="57"/>
       <c r="J7" s="57"/>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="57"/>
       <c r="C8" s="57"/>
       <c r="D8" s="57"/>
@@ -1592,7 +1604,7 @@
       <c r="I8" s="57"/>
       <c r="J8" s="57"/>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
@@ -1603,7 +1615,7 @@
       <c r="I9" s="57"/>
       <c r="J9" s="57"/>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="57"/>
       <c r="C10" s="57"/>
       <c r="D10" s="57"/>
@@ -1614,7 +1626,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
       <c r="D11" s="57"/>
@@ -1625,7 +1637,7 @@
       <c r="I11" s="57"/>
       <c r="J11" s="57"/>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
       <c r="D12" s="57"/>
@@ -1649,9 +1661,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="55" t="s">
         <v>2</v>
       </c>
@@ -1664,7 +1676,7 @@
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1675,7 +1687,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="56" t="s">
         <v>3</v>
       </c>
@@ -1688,7 +1700,7 @@
       <c r="I4" s="56"/>
       <c r="J4" s="56"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
       <c r="D5" s="56"/>
@@ -1699,7 +1711,7 @@
       <c r="I5" s="56"/>
       <c r="J5" s="56"/>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="56"/>
       <c r="C6" s="56"/>
       <c r="D6" s="56"/>
@@ -1710,7 +1722,7 @@
       <c r="I6" s="56"/>
       <c r="J6" s="56"/>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1721,7 +1733,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
         <v>4</v>
@@ -1734,7 +1746,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="58" t="s">
         <v>5</v>
@@ -1747,7 +1759,7 @@
       <c r="I9" s="58"/>
       <c r="J9" s="58"/>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="48"/>
       <c r="C10" s="58" t="s">
         <v>6</v>
@@ -1760,7 +1772,7 @@
       <c r="I10" s="58"/>
       <c r="J10" s="58"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="49"/>
       <c r="C11" s="52" t="s">
         <v>7</v>
@@ -1773,7 +1785,7 @@
       <c r="I11" s="52"/>
       <c r="J11" s="52"/>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="58" t="s">
         <v>8</v>
@@ -1801,13 +1813,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C2" s="55" t="s">
         <v>9</v>
       </c>
@@ -1825,7 +1837,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="56" t="s">
         <v>10</v>
       </c>
@@ -1843,7 +1855,7 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1859,7 +1871,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C6" s="53" t="s">
         <v>11</v>
       </c>
@@ -1882,7 +1894,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C7" s="53"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
@@ -1893,7 +1905,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1916,7 +1928,7 @@
       <c r="O9" s="54"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -1963,7 +1975,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -2012,7 +2024,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -2061,7 +2073,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -2108,7 +2120,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -2155,7 +2167,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -2204,7 +2216,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -2253,7 +2265,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -2302,7 +2314,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -2351,7 +2363,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -2398,7 +2410,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -2445,7 +2457,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -2494,7 +2506,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -2543,7 +2555,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -2592,7 +2604,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -2641,7 +2653,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -2690,7 +2702,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -2739,7 +2751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -2786,7 +2798,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -2833,7 +2845,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -2880,7 +2892,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -2927,7 +2939,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -2978,7 +2990,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:16" ht="15">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -3029,7 +3041,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="2:16" ht="15">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -3080,7 +3092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="2:16" ht="15">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -3131,7 +3143,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="15">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -3182,7 +3194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -3229,7 +3241,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -3276,7 +3288,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -3327,7 +3339,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -3378,7 +3390,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -3429,7 +3441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -3480,7 +3492,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -3531,7 +3543,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -3578,7 +3590,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -3625,7 +3637,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -3676,7 +3688,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="2:16" ht="15">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -3727,7 +3739,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="2:16" ht="15">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -3778,7 +3790,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="2:16" ht="15">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -3829,7 +3841,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="15">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -3880,7 +3892,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -3931,7 +3943,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -3982,7 +3994,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -4033,7 +4045,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -4084,7 +4096,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -4135,7 +4147,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -4182,7 +4194,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -4229,7 +4241,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -4280,7 +4292,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -4331,7 +4343,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -4382,7 +4394,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -4433,7 +4445,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -4484,7 +4496,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -4535,7 +4547,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -4586,7 +4598,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -4637,7 +4649,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -4688,7 +4700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -4739,7 +4751,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -4768,7 +4780,7 @@
       </c>
       <c r="K67" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="L67" s="47">
         <v>3</v>
@@ -4786,7 +4798,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -4815,7 +4827,7 @@
       </c>
       <c r="K68" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L68" s="47">
         <v>0.5</v>
@@ -4833,7 +4845,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -4864,7 +4876,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -4895,7 +4907,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -4926,7 +4938,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -4957,7 +4969,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -4988,7 +5000,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -5019,7 +5031,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -5050,7 +5062,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -5081,7 +5093,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -5112,7 +5124,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -5143,7 +5155,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -5174,7 +5186,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -5205,7 +5217,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -5236,7 +5248,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -5267,7 +5279,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -5298,7 +5310,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -5329,7 +5341,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -5360,7 +5372,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -5391,7 +5403,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -5422,7 +5434,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -5453,7 +5465,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -5484,7 +5496,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -5515,7 +5527,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -5546,7 +5558,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -5577,7 +5589,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -5608,7 +5620,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -5639,7 +5651,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -5670,7 +5682,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -5701,7 +5713,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -5732,7 +5744,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -5763,7 +5775,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -5794,7 +5806,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -5825,7 +5837,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -5856,7 +5868,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -5887,7 +5899,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -5918,7 +5930,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -5949,7 +5961,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -5980,7 +5992,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -6011,7 +6023,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -6042,7 +6054,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -6073,7 +6085,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -6104,7 +6116,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -6150,7 +6162,7 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20 J11:J15 J69:J110">
+  <conditionalFormatting sqref="J11:J15 J20 J69:J110">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
@@ -6223,13 +6235,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C2" s="55" t="s">
         <v>108</v>
       </c>
@@ -6247,7 +6259,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="56" t="s">
         <v>10</v>
       </c>
@@ -6265,7 +6277,7 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6281,7 +6293,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C6" s="53" t="s">
         <v>11</v>
       </c>
@@ -6290,7 +6302,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -6304,18 +6316,18 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C7" s="53"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>0</v>
+        <v>322.49999600000001</v>
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -6338,7 +6350,7 @@
       <c r="O9" s="54"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -6385,224 +6397,344 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="41">
         <v>1</v>
       </c>
       <c r="C11" s="42" t="str">
         <f>IF(ISBLANK(D11), "", _xlfn.CONCAT("T", TEXT(B11, "0000"), "/", VLOOKUP(D11, Internal!$B$35:C$39, 2, FALSE), IF(OR(D11="QA", D11="Revision"), _xlfn.CONCAT("/", H11), "")))</f>
-        <v/>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
+        <v>T0001/M</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H11" s="43"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="I11" s="46">
+        <v>46125.6875</v>
+      </c>
+      <c r="J11" s="46">
+        <v>46125.729166666664</v>
+      </c>
       <c r="K11" s="45" t="str">
         <f ca="1">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L11" s="47">
+        <v>1</v>
+      </c>
+      <c r="M11" s="47">
+        <v>1</v>
+      </c>
+      <c r="N11" s="45">
         <f>IF(ISBLANK(L11), "", L11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O11" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O11" s="45">
         <f>IF(ISBLANK(M11), "", M11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P11" s="44"/>
-    </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1">
+        <v>50</v>
+      </c>
+      <c r="P11" s="44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="41">
         <v>2</v>
       </c>
       <c r="C12" s="42" t="str">
         <f>IF(ISBLANK(D12), "", _xlfn.CONCAT("T", TEXT(B12, "0000"), "/", VLOOKUP(D12, Internal!$B$35:C$39, 2, FALSE), IF(OR(D12="QA", D12="Revision"), _xlfn.CONCAT("/", H12), "")))</f>
-        <v/>
-      </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+        <v>T0002/M</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="I12" s="46">
+        <v>46125.8125</v>
+      </c>
+      <c r="J12" s="46">
+        <v>46125.854166666664</v>
+      </c>
       <c r="K12" s="45" t="str">
         <f t="shared" ref="K12:K75" ca="1" si="0">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L12" s="47">
+        <v>1</v>
+      </c>
+      <c r="M12" s="47">
+        <v>1</v>
+      </c>
+      <c r="N12" s="45">
         <f>IF(ISBLANK(L12), "", L12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O12" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O12" s="45">
         <f>IF(ISBLANK(M12), "", M12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P12" s="44"/>
-    </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1">
+        <v>50</v>
+      </c>
+      <c r="P12" s="44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="41">
         <v>3</v>
       </c>
       <c r="C13" s="42" t="str">
         <f>IF(ISBLANK(D13), "", _xlfn.CONCAT("T", TEXT(B13, "0000"), "/", VLOOKUP(D13, Internal!$B$35:C$39, 2, FALSE), IF(OR(D13="QA", D13="Revision"), _xlfn.CONCAT("/", H13), "")))</f>
-        <v/>
-      </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="44"/>
+        <v>T0003/M</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>127</v>
+      </c>
       <c r="H13" s="43"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="I13" s="46">
+        <v>46132.763888888891</v>
+      </c>
+      <c r="J13" s="46">
+        <v>46132.819444444445</v>
+      </c>
       <c r="K13" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L13" s="47">
+        <v>1</v>
+      </c>
+      <c r="M13" s="47">
+        <v>1.3333333000000001</v>
+      </c>
+      <c r="N13" s="45">
         <f>IF(ISBLANK(L13), "", L13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O13" s="45" t="str">
+        <v>40</v>
+      </c>
+      <c r="O13" s="45">
         <f>IF(ISBLANK(M13), "", M13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>53.333331999999999</v>
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="41">
         <v>4</v>
       </c>
       <c r="C14" s="42" t="str">
         <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
-        <v/>
-      </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
+        <v>T0004/M</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>40</v>
+      </c>
       <c r="H14" s="43"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
+      <c r="I14" s="46">
+        <v>46132.819444444445</v>
+      </c>
+      <c r="J14" s="46">
+        <v>46132.847222222219</v>
+      </c>
       <c r="K14" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L14" s="47">
+        <v>1</v>
+      </c>
+      <c r="M14" s="47">
+        <v>0.6666666</v>
+      </c>
+      <c r="N14" s="45">
         <f>IF(ISBLANK(L14), "", L14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O14" s="45" t="str">
+        <v>40</v>
+      </c>
+      <c r="O14" s="45">
         <f>IF(ISBLANK(M14), "", M14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>26.666664000000001</v>
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="41">
         <v>5</v>
       </c>
       <c r="C15" s="42" t="str">
         <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
-        <v/>
-      </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
+        <v>T0005/M</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="I15" s="46">
+        <v>46132.833333333336</v>
+      </c>
+      <c r="J15" s="46">
+        <v>46132.916666666664</v>
+      </c>
       <c r="K15" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L15" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="47">
+        <v>2</v>
+      </c>
+      <c r="N15" s="45">
         <f>IF(ISBLANK(L15), "", L15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O15" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O15" s="45">
         <f>IF(ISBLANK(M15), "", M15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="41">
         <v>6</v>
       </c>
       <c r="C16" s="42" t="str">
         <f>IF(ISBLANK(D16), "", _xlfn.CONCAT("T", TEXT(B16, "0000"), "/", VLOOKUP(D16, Internal!$B$35:C$39, 2, FALSE), IF(OR(D16="QA", D16="Revision"), _xlfn.CONCAT("/", H16), "")))</f>
-        <v/>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="44"/>
+        <v>T0006/D</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H16" s="43"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="46">
+        <v>46136.5</v>
+      </c>
+      <c r="J16" s="46">
+        <v>46136.541666666664</v>
+      </c>
       <c r="K16" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L16" s="47">
+        <v>2</v>
+      </c>
+      <c r="M16" s="47">
+        <v>1</v>
+      </c>
+      <c r="N16" s="45">
         <f>IF(ISBLANK(L16), "", L16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O16" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O16" s="45">
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="41">
         <v>7</v>
       </c>
       <c r="C17" s="42" t="str">
         <f>IF(ISBLANK(D17), "", _xlfn.CONCAT("T", TEXT(B17, "0000"), "/", VLOOKUP(D17, Internal!$B$35:C$39, 2, FALSE), IF(OR(D17="QA", D17="Revision"), _xlfn.CONCAT("/", H17), "")))</f>
-        <v/>
-      </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
+        <v>T0007/M</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>40</v>
+      </c>
       <c r="H17" s="43"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
+      <c r="I17" s="46">
+        <v>46136.5625</v>
+      </c>
+      <c r="J17" s="46">
+        <v>46136.59375</v>
+      </c>
       <c r="K17" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L17" s="47">
+        <v>1</v>
+      </c>
+      <c r="M17" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="N17" s="45">
         <f>IF(ISBLANK(L17), "", L17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O17" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O17" s="45">
         <f>IF(ISBLANK(M17), "", M17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>37.5</v>
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -6633,7 +6765,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -6664,7 +6796,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -6695,7 +6827,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -6726,7 +6858,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -6757,7 +6889,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -6788,7 +6920,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -6819,7 +6951,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -6850,7 +6982,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -6881,7 +7013,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -6912,7 +7044,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1">
+    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -6943,7 +7075,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1">
+    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -6974,7 +7106,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1">
+    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -7005,7 +7137,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1">
+    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -7036,7 +7168,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1">
+    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -7067,7 +7199,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1">
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -7098,7 +7230,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -7129,7 +7261,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1">
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -7160,7 +7292,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -7191,7 +7323,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -7222,7 +7354,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -7253,7 +7385,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -7284,7 +7416,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -7315,7 +7447,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -7346,7 +7478,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -7377,7 +7509,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -7408,7 +7540,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -7439,7 +7571,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -7470,7 +7602,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -7501,7 +7633,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -7532,7 +7664,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -7563,7 +7695,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -7594,7 +7726,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -7625,7 +7757,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -7656,7 +7788,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -7687,7 +7819,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -7718,7 +7850,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -7749,7 +7881,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -7780,7 +7912,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -7811,7 +7943,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -7842,7 +7974,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -7873,7 +8005,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -7904,7 +8036,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -7935,7 +8067,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -7966,7 +8098,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -7997,7 +8129,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -8028,7 +8160,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -8059,7 +8191,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -8090,7 +8222,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -8121,7 +8253,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -8152,7 +8284,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -8183,7 +8315,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -8214,7 +8346,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -8245,7 +8377,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -8276,7 +8408,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -8307,7 +8439,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -8338,7 +8470,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -8369,7 +8501,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -8400,7 +8532,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -8431,7 +8563,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -8462,7 +8594,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -8493,7 +8625,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -8524,7 +8656,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -8555,7 +8687,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -8586,7 +8718,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -8617,7 +8749,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -8648,7 +8780,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -8679,7 +8811,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -8710,7 +8842,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -8741,7 +8873,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -8772,7 +8904,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -8803,7 +8935,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -8834,7 +8966,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -8865,7 +8997,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -8896,7 +9028,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -8927,7 +9059,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -8958,7 +9090,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -8989,7 +9121,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -9020,7 +9152,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -9051,7 +9183,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -9082,7 +9214,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -9113,7 +9245,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -9144,7 +9276,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -9175,7 +9307,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -9206,7 +9338,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -9237,7 +9369,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -9268,7 +9400,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -9299,7 +9431,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -9330,7 +9462,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -9361,7 +9493,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -9392,7 +9524,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -9423,7 +9555,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -9454,7 +9586,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -9499,9 +9631,9 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J110">
+  <conditionalFormatting sqref="J18:J110">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
+      <formula>AND(I18&lt;&gt;"",J18&lt;&gt;"", I18&gt;J18)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
@@ -9552,7 +9684,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J110</xm:sqref>
+          <xm:sqref>J18:J110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Start moment" prompt="Indicate the moment when the assignee starts working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{175B319B-7D79-46C0-980E-ECB0D923AF19}">
           <x14:formula1>
@@ -9561,7 +9693,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>I11:I110</xm:sqref>
+          <xm:sqref>J11:J17 I11:I110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9572,13 +9704,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C2" s="55" t="s">
         <v>109</v>
       </c>
@@ -9596,7 +9728,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="56" t="s">
         <v>10</v>
       </c>
@@ -9614,7 +9746,7 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -9630,7 +9762,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C6" s="53" t="s">
         <v>11</v>
       </c>
@@ -9653,7 +9785,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C7" s="53"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
@@ -9664,7 +9796,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -9687,7 +9819,7 @@
       <c r="O9" s="54"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -9734,7 +9866,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -9765,7 +9897,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -9796,7 +9928,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -9827,7 +9959,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -9858,7 +9990,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -9889,7 +10021,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -9920,7 +10052,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -9951,7 +10083,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -9982,7 +10114,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -10013,7 +10145,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -10044,7 +10176,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -10075,7 +10207,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -10106,7 +10238,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -10137,7 +10269,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -10168,7 +10300,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -10199,7 +10331,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -10230,7 +10362,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -10261,7 +10393,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1">
+    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -10292,7 +10424,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1">
+    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -10323,7 +10455,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1">
+    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -10354,7 +10486,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1">
+    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -10385,7 +10517,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1">
+    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -10416,7 +10548,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1">
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -10447,7 +10579,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -10478,7 +10610,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1">
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -10509,7 +10641,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -10540,7 +10672,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -10571,7 +10703,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -10602,7 +10734,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -10633,7 +10765,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -10664,7 +10796,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -10695,7 +10827,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -10726,7 +10858,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -10757,7 +10889,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -10788,7 +10920,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -10819,7 +10951,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -10850,7 +10982,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -10881,7 +11013,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -10912,7 +11044,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -10943,7 +11075,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -10974,7 +11106,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -11005,7 +11137,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -11036,7 +11168,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -11067,7 +11199,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -11098,7 +11230,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -11129,7 +11261,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -11160,7 +11292,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -11191,7 +11323,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -11222,7 +11354,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -11253,7 +11385,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -11284,7 +11416,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -11315,7 +11447,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -11346,7 +11478,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -11377,7 +11509,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -11408,7 +11540,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -11439,7 +11571,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -11470,7 +11602,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -11501,7 +11633,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -11532,7 +11664,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -11563,7 +11695,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -11594,7 +11726,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -11625,7 +11757,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -11656,7 +11788,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -11687,7 +11819,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -11718,7 +11850,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -11749,7 +11881,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -11780,7 +11912,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -11811,7 +11943,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -11842,7 +11974,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -11873,7 +12005,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -11904,7 +12036,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -11935,7 +12067,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -11966,7 +12098,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -11997,7 +12129,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -12028,7 +12160,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -12059,7 +12191,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -12090,7 +12222,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -12121,7 +12253,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -12152,7 +12284,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -12183,7 +12315,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -12214,7 +12346,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -12245,7 +12377,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -12276,7 +12408,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -12307,7 +12439,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -12338,7 +12470,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -12369,7 +12501,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -12400,7 +12532,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -12431,7 +12563,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -12462,7 +12594,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -12493,7 +12625,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -12524,7 +12656,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -12555,7 +12687,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -12586,7 +12718,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -12617,7 +12749,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -12648,7 +12780,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -12679,7 +12811,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -12710,7 +12842,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -12741,7 +12873,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -12772,7 +12904,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -12803,7 +12935,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -12921,12 +13053,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="55" t="s">
         <v>110</v>
       </c>
@@ -12939,7 +13071,7 @@
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="56" t="s">
         <v>111</v>
       </c>
@@ -12952,7 +13084,7 @@
       <c r="I4" s="56"/>
       <c r="J4" s="56"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
       <c r="D5" s="56"/>
@@ -12963,7 +13095,7 @@
       <c r="I5" s="56"/>
       <c r="J5" s="56"/>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="56"/>
       <c r="C6" s="56"/>
       <c r="D6" s="56"/>
@@ -12974,7 +13106,7 @@
       <c r="I6" s="56"/>
       <c r="J6" s="56"/>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -12985,7 +13117,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
         <v>112</v>
       </c>
@@ -12998,7 +13130,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
@@ -13011,7 +13143,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
@@ -13024,7 +13156,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>61</v>
       </c>
@@ -13037,7 +13169,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
@@ -13050,7 +13182,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
@@ -13063,7 +13195,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
@@ -13076,7 +13208,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -13087,7 +13219,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="26" t="s">
         <v>113</v>
       </c>
@@ -13100,7 +13232,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
         <v>114</v>
       </c>
@@ -13113,7 +13245,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="s">
         <v>115</v>
       </c>
@@ -13126,7 +13258,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
         <v>116</v>
       </c>
@@ -13139,7 +13271,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -13150,7 +13282,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="26" t="s">
         <v>117</v>
       </c>
@@ -13163,7 +13295,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="17">
         <v>45658</v>
       </c>
@@ -13176,7 +13308,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
         <v>118</v>
       </c>
@@ -13189,7 +13321,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -13200,7 +13332,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="27" t="s">
         <v>119</v>
       </c>
@@ -13217,7 +13349,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="19" t="s">
         <v>56</v>
       </c>
@@ -13240,7 +13372,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="19" t="s">
         <v>32</v>
       </c>
@@ -13267,7 +13399,7 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="19" t="s">
         <v>126</v>
       </c>
@@ -13292,7 +13424,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="19" t="s">
         <v>38</v>
       </c>
@@ -13319,7 +13451,7 @@
       </c>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="19" t="s">
         <v>51</v>
       </c>
@@ -13346,7 +13478,7 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="21" t="s">
         <v>105</v>
       </c>
@@ -13375,7 +13507,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="22" t="s">
         <v>54</v>
       </c>
@@ -13392,7 +13524,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="24"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -13403,7 +13535,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="33" t="s">
         <v>137</v>
       </c>
@@ -13418,7 +13550,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="21" t="s">
         <v>30</v>
       </c>
@@ -13433,7 +13565,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="21" t="s">
         <v>35</v>
       </c>
@@ -13448,7 +13580,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="21" t="s">
         <v>49</v>
       </c>
@@ -13463,7 +13595,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="21" t="s">
         <v>141</v>
       </c>
@@ -13478,7 +13610,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="32" t="s">
         <v>54</v>
       </c>

--- a/reports/Planning Report.xlsx
+++ b/reports/Planning Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZMis_cosas\UNI\DP2_2026\Workspace-26\Projects\Acme-Starters-B\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eramo\Desktop\Tercero\DP2\Proyecto\Workspace-26\Workspace-26\Projects\Acme-Starters-B\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D25F628-DEFE-49A4-9EE7-4C8B69EDEC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEC8CA6-E22F-47B7-A2FC-421B8DF14CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="170">
   <si>
     <t>Copyright</t>
   </si>
@@ -503,6 +503,72 @@
   </si>
   <si>
     <t>T0003/M</t>
+  </si>
+  <si>
+    <t>Create project class requirements B2</t>
+  </si>
+  <si>
+    <t>Create AdBanners requirements B5</t>
+  </si>
+  <si>
+    <t>Display ad banners B12</t>
+  </si>
+  <si>
+    <t>Review B5 y B12</t>
+  </si>
+  <si>
+    <t>T0008/D</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Create member squad and Multiplicities &amp; Constraints B3 y B4</t>
+  </si>
+  <si>
+    <t>T0009/D</t>
+  </si>
+  <si>
+    <t>Populate sample data of Project, Member and WorksIn</t>
+  </si>
+  <si>
+    <t>Feature list project and their components of member's projects B6</t>
+  </si>
+  <si>
+    <t>Feature Dashoard B11</t>
+  </si>
+  <si>
+    <t>T0018/D</t>
+  </si>
+  <si>
+    <t>Fix views and repository dashboard</t>
+  </si>
+  <si>
+    <t>Feature list project and their components of managers's projects B10</t>
+  </si>
+  <si>
+    <t>Feature of views Any, Authenticated and CRUD manager B8, B9 y B10</t>
+  </si>
+  <si>
+    <t>T0022/D</t>
+  </si>
+  <si>
+    <t>Review B10</t>
+  </si>
+  <si>
+    <t>Review B8 y B9</t>
+  </si>
+  <si>
+    <t>And view members in Member and Manager</t>
+  </si>
+  <si>
+    <t>Fix dashboard</t>
+  </si>
+  <si>
+    <t>Add and delete memebers of a project</t>
+  </si>
+  <si>
+    <t>Views members in Any-Authenticated and fix in this views but in Member and Manager</t>
   </si>
 </sst>
 </file>
@@ -879,17 +945,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1529,26 +1595,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BB59C7-21D2-4063-B60E-B9743CBEBCDD}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="56" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B4" s="54" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="57"/>
@@ -1560,7 +1626,7 @@
       <c r="I4" s="57"/>
       <c r="J4" s="57"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="57"/>
       <c r="C5" s="57"/>
       <c r="D5" s="57"/>
@@ -1571,7 +1637,7 @@
       <c r="I5" s="57"/>
       <c r="J5" s="57"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="57"/>
       <c r="C6" s="57"/>
       <c r="D6" s="57"/>
@@ -1582,7 +1648,7 @@
       <c r="I6" s="57"/>
       <c r="J6" s="57"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="57"/>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
@@ -1593,7 +1659,7 @@
       <c r="I7" s="57"/>
       <c r="J7" s="57"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="57"/>
       <c r="C8" s="57"/>
       <c r="D8" s="57"/>
@@ -1604,7 +1670,7 @@
       <c r="I8" s="57"/>
       <c r="J8" s="57"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
@@ -1615,7 +1681,7 @@
       <c r="I9" s="57"/>
       <c r="J9" s="57"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="57"/>
       <c r="C10" s="57"/>
       <c r="D10" s="57"/>
@@ -1626,7 +1692,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
       <c r="D11" s="57"/>
@@ -1637,7 +1703,7 @@
       <c r="I11" s="57"/>
       <c r="J11" s="57"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
       <c r="D12" s="57"/>
@@ -1661,22 +1727,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1687,42 +1753,42 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="56" t="s">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1733,7 +1799,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
         <v>4</v>
@@ -1746,7 +1812,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="C9" s="58" t="s">
         <v>5</v>
@@ -1759,7 +1825,7 @@
       <c r="I9" s="58"/>
       <c r="J9" s="58"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="48"/>
       <c r="C10" s="58" t="s">
         <v>6</v>
@@ -1772,7 +1838,7 @@
       <c r="I10" s="58"/>
       <c r="J10" s="58"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="49"/>
       <c r="C11" s="52" t="s">
         <v>7</v>
@@ -1785,7 +1851,7 @@
       <c r="I11" s="52"/>
       <c r="J11" s="52"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="58" t="s">
         <v>8</v>
@@ -1813,49 +1879,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="55" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1871,8 +1937,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1894,8 +1960,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="53"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
@@ -1905,7 +1971,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1913,22 +1979,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="54" t="s">
+      <c r="L9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="54"/>
+      <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -1975,7 +2041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -2024,7 +2090,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -2073,7 +2139,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -2120,7 +2186,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -2167,7 +2233,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -2216,7 +2282,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -2265,7 +2331,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -2314,7 +2380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -2363,7 +2429,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -2410,7 +2476,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -2457,7 +2523,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -2506,7 +2572,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -2555,7 +2621,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -2604,7 +2670,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -2653,7 +2719,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -2702,7 +2768,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -2751,7 +2817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -2798,7 +2864,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -2845,7 +2911,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -2892,7 +2958,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -2939,7 +3005,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -2990,7 +3056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -3041,7 +3107,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -3092,7 +3158,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -3143,7 +3209,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -3194,7 +3260,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -3241,7 +3307,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -3288,7 +3354,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -3339,7 +3405,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -3390,7 +3456,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -3441,7 +3507,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -3492,7 +3558,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -3543,7 +3609,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -3590,7 +3656,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -3637,7 +3703,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -3688,7 +3754,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -3739,7 +3805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -3790,7 +3856,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -3841,7 +3907,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -3892,7 +3958,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -3943,7 +4009,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -3994,7 +4060,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -4045,7 +4111,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -4096,7 +4162,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -4147,7 +4213,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -4194,7 +4260,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -4241,7 +4307,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -4292,7 +4358,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -4343,7 +4409,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -4394,7 +4460,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -4445,7 +4511,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -4496,7 +4562,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -4547,7 +4613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -4598,7 +4664,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -4649,7 +4715,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -4700,7 +4766,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -4751,7 +4817,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -4798,7 +4864,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -4845,7 +4911,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -4876,7 +4942,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -4907,7 +4973,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -4938,7 +5004,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -4969,7 +5035,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -5000,7 +5066,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -5031,7 +5097,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -5062,7 +5128,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -5093,7 +5159,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -5124,7 +5190,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -5155,7 +5221,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -5186,7 +5252,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -5217,7 +5283,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -5248,7 +5314,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -5279,7 +5345,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -5310,7 +5376,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -5341,7 +5407,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -5372,7 +5438,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -5403,7 +5469,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -5434,7 +5500,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -5465,7 +5531,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -5496,7 +5562,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -5527,7 +5593,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -5558,7 +5624,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -5589,7 +5655,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -5620,7 +5686,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -5651,7 +5717,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -5682,7 +5748,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -5713,7 +5779,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -5744,7 +5810,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -5775,7 +5841,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -5806,7 +5872,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -5837,7 +5903,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -5868,7 +5934,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -5899,7 +5965,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -5930,7 +5996,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -5961,7 +6027,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -5992,7 +6058,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -6023,7 +6089,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -6054,7 +6120,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -6085,7 +6151,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -6116,7 +6182,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -6235,49 +6301,49 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="55" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C2" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6293,8 +6359,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -6302,7 +6368,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>340</v>
+        <v>1563.75</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -6316,18 +6382,18 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="53"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>322.49999600000001</v>
+        <v>1689.999996</v>
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -6335,22 +6401,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="54" t="s">
+      <c r="L9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="54"/>
+      <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -6397,7 +6463,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -6446,7 +6512,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -6497,7 +6563,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -6544,7 +6610,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -6591,7 +6657,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -6640,7 +6706,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -6685,9 +6751,11 @@
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>25</v>
       </c>
-      <c r="P16" s="44"/>
-    </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P16" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -6734,774 +6802,1222 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="41">
         <v>8</v>
       </c>
       <c r="C18" s="42" t="str">
         <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
-        <v/>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
+        <v>T0008/D</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H18" s="43"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
+      <c r="I18" s="46">
+        <v>46136.416666666664</v>
+      </c>
+      <c r="J18" s="46">
+        <v>46136.496527777781</v>
+      </c>
       <c r="K18" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L18" s="47">
+        <v>1</v>
+      </c>
+      <c r="M18" s="47">
+        <v>1</v>
+      </c>
+      <c r="N18" s="45">
         <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O18" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O18" s="45">
         <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P18" s="44"/>
-    </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="41">
         <v>9</v>
       </c>
       <c r="C19" s="42" t="str">
         <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
-        <v/>
-      </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
+        <v>T0009/D</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H19" s="43"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="I19" s="46">
+        <v>46137.375</v>
+      </c>
+      <c r="J19" s="46">
+        <v>46137.75</v>
+      </c>
       <c r="K19" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L19" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M19" s="47">
+        <v>1</v>
+      </c>
+      <c r="N19" s="45">
         <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O19" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O19" s="45">
         <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P19" s="44"/>
-    </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="P19" s="44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="41">
         <v>10</v>
       </c>
       <c r="C20" s="42" t="str">
         <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
-        <v/>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+        <v>T0010/R/T0009/D</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="I20" s="46">
+        <v>46138.5</v>
+      </c>
+      <c r="J20" s="46">
+        <v>46138.510416666664</v>
+      </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L20" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N20" s="45">
         <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O20" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O20" s="45">
         <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P20" s="44"/>
-    </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>6.25</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="41">
         <v>11</v>
       </c>
       <c r="C21" s="42" t="str">
         <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
-        <v/>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
+        <v>T0011/D</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" s="46">
+        <v>46138.520833333336</v>
+      </c>
+      <c r="J21" s="46">
+        <v>46138.583333333336</v>
+      </c>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L21" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M21" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O21" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O21" s="45">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P21" s="44"/>
-    </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37.5</v>
+      </c>
+      <c r="P21" s="44" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="41">
         <v>12</v>
       </c>
       <c r="C22" s="42" t="str">
         <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
-        <v/>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
+        <v>T0012/QA/</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H22" s="43"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J22" s="46">
+        <v>46139.722222222219</v>
+      </c>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L22" s="47">
+        <v>2</v>
+      </c>
+      <c r="M22" s="47">
+        <v>2</v>
+      </c>
+      <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O22" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O22" s="45">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="41">
         <v>13</v>
       </c>
       <c r="C23" s="42" t="str">
         <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
-        <v/>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
+        <v>T0013/QA/T0008/D</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J23" s="46">
+        <v>46139.833333333336</v>
+      </c>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L23" s="47">
+        <v>2</v>
+      </c>
+      <c r="M23" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="N23" s="45">
         <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O23" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O23" s="45">
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P23" s="44"/>
-    </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="P23" s="44" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="41">
         <v>14</v>
       </c>
       <c r="C24" s="42" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v/>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+        <v>T0014/D</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H24" s="43"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="46">
+        <v>46140.375</v>
+      </c>
+      <c r="J24" s="46">
+        <v>46141.722222222219</v>
+      </c>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L24" s="47">
+        <v>5</v>
+      </c>
+      <c r="M24" s="47">
+        <v>5</v>
+      </c>
+      <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O24" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O24" s="45">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P24" s="44"/>
-    </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="P24" s="44" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="41">
         <v>15</v>
       </c>
       <c r="C25" s="42" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
+        <v>T0015/R/T0014/D</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="46">
+        <v>46141.520833333336</v>
+      </c>
+      <c r="J25" s="46">
+        <v>46141.53125</v>
+      </c>
       <c r="K25" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L25" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O25" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O25" s="45">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>6.25</v>
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="41">
         <v>16</v>
       </c>
       <c r="C26" s="42" t="str">
         <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
-        <v/>
-      </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
+        <v>T0016/D</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H26" s="43"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
+      <c r="I26" s="46">
+        <v>46142.416666666664</v>
+      </c>
+      <c r="J26" s="46">
+        <v>46143.833333333336</v>
+      </c>
       <c r="K26" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L26" s="47">
+        <v>3</v>
+      </c>
+      <c r="M26" s="47">
+        <v>4</v>
+      </c>
+      <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O26" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O26" s="45">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P26" s="44"/>
-    </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="P26" s="44" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="41">
         <v>17</v>
       </c>
       <c r="C27" s="42" t="str">
         <f>IF(ISBLANK(D27), "", _xlfn.CONCAT("T", TEXT(B27, "0000"), "/", VLOOKUP(D27, Internal!$B$35:C$39, 2, FALSE), IF(OR(D27="QA", D27="Revision"), _xlfn.CONCAT("/", H27), "")))</f>
-        <v/>
-      </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="44"/>
+        <v>T0017/QA/</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H27" s="43"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
+      <c r="I27" s="46">
+        <v>46142.736111111109</v>
+      </c>
+      <c r="J27" s="46">
+        <v>46142.8125</v>
+      </c>
       <c r="K27" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L27" s="47">
+        <v>2</v>
+      </c>
+      <c r="M27" s="47">
+        <v>2</v>
+      </c>
+      <c r="N27" s="45">
         <f>IF(ISBLANK(L27), "", L27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O27" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O27" s="45">
         <f>IF(ISBLANK(M27), "", M27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="41">
         <v>18</v>
       </c>
       <c r="C28" s="42" t="str">
         <f>IF(ISBLANK(D28), "", _xlfn.CONCAT("T", TEXT(B28, "0000"), "/", VLOOKUP(D28, Internal!$B$35:C$39, 2, FALSE), IF(OR(D28="QA", D28="Revision"), _xlfn.CONCAT("/", H28), "")))</f>
-        <v/>
-      </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
+        <v>T0018/D</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H28" s="43"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
+      <c r="I28" s="46">
+        <v>46142.833333333336</v>
+      </c>
+      <c r="J28" s="46">
+        <v>46143.5</v>
+      </c>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L28" s="47">
+        <v>4</v>
+      </c>
+      <c r="M28" s="47">
+        <v>5</v>
+      </c>
+      <c r="N28" s="45">
         <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O28" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O28" s="45">
         <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P28" s="44"/>
-    </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="P28" s="44" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="41">
         <v>19</v>
       </c>
       <c r="C29" s="42" t="str">
         <f>IF(ISBLANK(D29), "", _xlfn.CONCAT("T", TEXT(B29, "0000"), "/", VLOOKUP(D29, Internal!$B$35:C$39, 2, FALSE), IF(OR(D29="QA", D29="Revision"), _xlfn.CONCAT("/", H29), "")))</f>
-        <v/>
-      </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
+        <v>T0019/D</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="46">
+        <v>46144.375</v>
+      </c>
+      <c r="J29" s="46">
+        <v>46144.385416666664</v>
+      </c>
       <c r="K29" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L29" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N29" s="45">
         <f>IF(ISBLANK(L29), "", L29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O29" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O29" s="45">
         <f>IF(ISBLANK(M29), "", M29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>6.25</v>
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="41">
         <v>20</v>
       </c>
       <c r="C30" s="42" t="str">
         <f>IF(ISBLANK(D30), "", _xlfn.CONCAT("T", TEXT(B30, "0000"), "/", VLOOKUP(D30, Internal!$B$35:C$39, 2, FALSE), IF(OR(D30="QA", D30="Revision"), _xlfn.CONCAT("/", H30), "")))</f>
-        <v/>
-      </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+        <v>T0020/D</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="I30" s="46">
+        <v>46144.5</v>
+      </c>
+      <c r="J30" s="46">
+        <v>46144.510416666664</v>
+      </c>
       <c r="K30" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L30" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M30" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N30" s="45">
         <f>IF(ISBLANK(L30), "", L30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O30" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O30" s="45">
         <f>IF(ISBLANK(M30), "", M30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>6.25</v>
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="41">
         <v>21</v>
       </c>
       <c r="C31" s="42" t="str">
         <f>IF(ISBLANK(D31), "", _xlfn.CONCAT("T", TEXT(B31, "0000"), "/", VLOOKUP(D31, Internal!$B$35:C$39, 2, FALSE), IF(OR(D31="QA", D31="Revision"), _xlfn.CONCAT("/", H31), "")))</f>
-        <v/>
-      </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
+        <v>T0021/D</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="46">
+        <v>46147.375</v>
+      </c>
+      <c r="J31" s="46">
+        <v>46147.5</v>
+      </c>
       <c r="K31" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L31" s="47">
+        <v>1</v>
+      </c>
+      <c r="M31" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N31" s="45">
         <f>IF(ISBLANK(L31), "", L31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O31" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O31" s="45">
         <f>IF(ISBLANK(M31), "", M31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P31" s="44"/>
-    </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37.5</v>
+      </c>
+      <c r="P31" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="41">
         <v>22</v>
       </c>
       <c r="C32" s="42" t="str">
         <f>IF(ISBLANK(D32), "", _xlfn.CONCAT("T", TEXT(B32, "0000"), "/", VLOOKUP(D32, Internal!$B$35:C$39, 2, FALSE), IF(OR(D32="QA", D32="Revision"), _xlfn.CONCAT("/", H32), "")))</f>
-        <v/>
-      </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
+        <v>T0022/D</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H32" s="43"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
+      <c r="I32" s="46">
+        <v>46145.416666666664</v>
+      </c>
+      <c r="J32" s="46">
+        <v>46146.958333333336</v>
+      </c>
       <c r="K32" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L32" s="47">
+        <v>5</v>
+      </c>
+      <c r="M32" s="47">
+        <v>7</v>
+      </c>
+      <c r="N32" s="45">
         <f>IF(ISBLANK(L32), "", L32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O32" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O32" s="45">
         <f>IF(ISBLANK(M32), "", M32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P32" s="44"/>
-    </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+      <c r="P32" s="44" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="41">
         <v>23</v>
       </c>
       <c r="C33" s="42" t="str">
         <f>IF(ISBLANK(D33), "", _xlfn.CONCAT("T", TEXT(B33, "0000"), "/", VLOOKUP(D33, Internal!$B$35:C$39, 2, FALSE), IF(OR(D33="QA", D33="Revision"), _xlfn.CONCAT("/", H33), "")))</f>
-        <v/>
-      </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+        <v>T0023/QA/</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H33" s="43"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
+      <c r="I33" s="46">
+        <v>46146.645833333336</v>
+      </c>
+      <c r="J33" s="46">
+        <v>46146.729166666664</v>
+      </c>
       <c r="K33" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L33" s="47">
+        <v>2</v>
+      </c>
+      <c r="M33" s="47">
+        <v>2</v>
+      </c>
+      <c r="N33" s="45">
         <f>IF(ISBLANK(L33), "", L33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O33" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O33" s="45">
         <f>IF(ISBLANK(M33), "", M33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="41">
         <v>24</v>
       </c>
       <c r="C34" s="42" t="str">
         <f>IF(ISBLANK(D34), "", _xlfn.CONCAT("T", TEXT(B34, "0000"), "/", VLOOKUP(D34, Internal!$B$35:C$39, 2, FALSE), IF(OR(D34="QA", D34="Revision"), _xlfn.CONCAT("/", H34), "")))</f>
-        <v/>
-      </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
+        <v>T0024/R/T0022/D</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="I34" s="46">
+        <v>46147.375</v>
+      </c>
+      <c r="J34" s="46">
+        <v>46147.458333333336</v>
+      </c>
       <c r="K34" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L34" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N34" s="45">
         <f>IF(ISBLANK(L34), "", L34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O34" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O34" s="45">
         <f>IF(ISBLANK(M34), "", M34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P34" s="44"/>
-    </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37.5</v>
+      </c>
+      <c r="P34" s="44" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="41">
         <v>25</v>
       </c>
       <c r="C35" s="42" t="str">
         <f>IF(ISBLANK(D35), "", _xlfn.CONCAT("T", TEXT(B35, "0000"), "/", VLOOKUP(D35, Internal!$B$35:C$39, 2, FALSE), IF(OR(D35="QA", D35="Revision"), _xlfn.CONCAT("/", H35), "")))</f>
-        <v/>
-      </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
+        <v>T0025/R/T0022/D</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="I35" s="46">
+        <v>46147.416666666664</v>
+      </c>
+      <c r="J35" s="46">
+        <v>46147.458333333336</v>
+      </c>
       <c r="K35" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L35" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="47">
+        <v>1</v>
+      </c>
+      <c r="N35" s="45">
         <f>IF(ISBLANK(L35), "", L35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O35" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O35" s="45">
         <f>IF(ISBLANK(M35), "", M35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P35" s="44"/>
-    </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="P35" s="44" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="41">
         <v>26</v>
       </c>
       <c r="C36" s="42" t="str">
         <f>IF(ISBLANK(D36), "", _xlfn.CONCAT("T", TEXT(B36, "0000"), "/", VLOOKUP(D36, Internal!$B$35:C$39, 2, FALSE), IF(OR(D36="QA", D36="Revision"), _xlfn.CONCAT("/", H36), "")))</f>
-        <v/>
-      </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+        <v>T0026/D</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
+      <c r="I36" s="46">
+        <v>46148.520833333336</v>
+      </c>
+      <c r="J36" s="46">
+        <v>46148.822916666664</v>
+      </c>
       <c r="K36" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L36" s="47">
+        <v>2</v>
+      </c>
+      <c r="M36" s="47">
+        <v>2.25</v>
+      </c>
+      <c r="N36" s="45">
         <f>IF(ISBLANK(L36), "", L36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O36" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O36" s="45">
         <f>IF(ISBLANK(M36), "", M36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P36" s="44"/>
-    </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>56.25</v>
+      </c>
+      <c r="P36" s="44" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="41">
         <v>27</v>
       </c>
       <c r="C37" s="42" t="str">
         <f>IF(ISBLANK(D37), "", _xlfn.CONCAT("T", TEXT(B37, "0000"), "/", VLOOKUP(D37, Internal!$B$35:C$39, 2, FALSE), IF(OR(D37="QA", D37="Revision"), _xlfn.CONCAT("/", H37), "")))</f>
-        <v/>
-      </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
+        <v>T0027/D</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H37" s="43"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
+      <c r="I37" s="46">
+        <v>46148.541666666664</v>
+      </c>
+      <c r="J37" s="46">
+        <v>46148.645833333336</v>
+      </c>
       <c r="K37" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L37" s="47"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L37" s="47">
+        <v>1</v>
+      </c>
+      <c r="M37" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="N37" s="45">
         <f>IF(ISBLANK(L37), "", L37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O37" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O37" s="45">
         <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P37" s="44"/>
-    </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>18.75</v>
+      </c>
+      <c r="P37" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="41">
         <v>28</v>
       </c>
       <c r="C38" s="42" t="str">
         <f>IF(ISBLANK(D38), "", _xlfn.CONCAT("T", TEXT(B38, "0000"), "/", VLOOKUP(D38, Internal!$B$35:C$39, 2, FALSE), IF(OR(D38="QA", D38="Revision"), _xlfn.CONCAT("/", H38), "")))</f>
-        <v/>
-      </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+        <v>T0028/D</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H38" s="43"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
+      <c r="I38" s="46">
+        <v>46148.645833333336</v>
+      </c>
+      <c r="J38" s="46">
+        <v>46150.166666666664</v>
+      </c>
       <c r="K38" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L38" s="47">
+        <v>5</v>
+      </c>
+      <c r="M38" s="47">
+        <v>8</v>
+      </c>
+      <c r="N38" s="45">
         <f>IF(ISBLANK(L38), "", L38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O38" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O38" s="45">
         <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P38" s="44"/>
-    </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="P38" s="44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="41">
         <v>29</v>
       </c>
       <c r="C39" s="42" t="str">
         <f>IF(ISBLANK(D39), "", _xlfn.CONCAT("T", TEXT(B39, "0000"), "/", VLOOKUP(D39, Internal!$B$35:C$39, 2, FALSE), IF(OR(D39="QA", D39="Revision"), _xlfn.CONCAT("/", H39), "")))</f>
-        <v/>
-      </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
+        <v>T0029/D</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H39" s="43"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
+      <c r="I39" s="46">
+        <v>46149.5</v>
+      </c>
+      <c r="J39" s="46">
+        <v>46149.958333333336</v>
+      </c>
       <c r="K39" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L39" s="47">
+        <v>3</v>
+      </c>
+      <c r="M39" s="47">
+        <v>4</v>
+      </c>
+      <c r="N39" s="45">
         <f>IF(ISBLANK(L39), "", L39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O39" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O39" s="45">
         <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P39" s="44"/>
-    </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="P39" s="44" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="41">
         <v>30</v>
       </c>
       <c r="C40" s="42" t="str">
         <f>IF(ISBLANK(D40), "", _xlfn.CONCAT("T", TEXT(B40, "0000"), "/", VLOOKUP(D40, Internal!$B$35:C$39, 2, FALSE), IF(OR(D40="QA", D40="Revision"), _xlfn.CONCAT("/", H40), "")))</f>
-        <v/>
-      </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="44"/>
+        <v>T0030/QA/</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H40" s="43"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
+      <c r="I40" s="46">
+        <v>46149.736111111109</v>
+      </c>
+      <c r="J40" s="46">
+        <v>46149.8125</v>
+      </c>
       <c r="K40" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L40" s="47"/>
-      <c r="M40" s="47"/>
-      <c r="N40" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L40" s="47">
+        <v>2</v>
+      </c>
+      <c r="M40" s="47">
+        <v>2</v>
+      </c>
+      <c r="N40" s="45">
         <f>IF(ISBLANK(L40), "", L40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O40" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O40" s="45">
         <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="41">
         <v>31</v>
       </c>
       <c r="C41" s="42" t="str">
         <f>IF(ISBLANK(D41), "", _xlfn.CONCAT("T", TEXT(B41, "0000"), "/", VLOOKUP(D41, Internal!$B$35:C$39, 2, FALSE), IF(OR(D41="QA", D41="Revision"), _xlfn.CONCAT("/", H41), "")))</f>
-        <v/>
-      </c>
-      <c r="D41" s="44"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
+        <v>T0031/R/</v>
+      </c>
+      <c r="D41" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>132</v>
+      </c>
       <c r="H41" s="43"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
+      <c r="I41" s="46">
+        <v>46150.375</v>
+      </c>
+      <c r="J41" s="46">
+        <v>46150.9375</v>
+      </c>
       <c r="K41" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L41" s="47"/>
-      <c r="M41" s="47"/>
-      <c r="N41" s="45" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="L41" s="47">
+        <v>5</v>
+      </c>
+      <c r="M41" s="47">
+        <v>6</v>
+      </c>
+      <c r="N41" s="45">
         <f>IF(ISBLANK(L41), "", L41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O41" s="45" t="str">
+        <v>150</v>
+      </c>
+      <c r="O41" s="45">
         <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="41">
         <v>32</v>
       </c>
       <c r="C42" s="42" t="str">
         <f>IF(ISBLANK(D42), "", _xlfn.CONCAT("T", TEXT(B42, "0000"), "/", VLOOKUP(D42, Internal!$B$35:C$39, 2, FALSE), IF(OR(D42="QA", D42="Revision"), _xlfn.CONCAT("/", H42), "")))</f>
-        <v/>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="44"/>
+        <v>T0032/R/</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>133</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
+      <c r="I42" s="46">
+        <v>46273.5</v>
+      </c>
+      <c r="J42" s="46">
+        <v>46273.9375</v>
+      </c>
       <c r="K42" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L42" s="47"/>
+        <v>Planned</v>
+      </c>
+      <c r="L42" s="47">
+        <v>4</v>
+      </c>
       <c r="M42" s="47"/>
-      <c r="N42" s="45" t="str">
+      <c r="N42" s="45">
         <f>IF(ISBLANK(L42), "", L42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="O42" s="45" t="str">
         <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
@@ -7509,24 +8025,36 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="41">
         <v>33</v>
       </c>
       <c r="C43" s="42" t="str">
         <f>IF(ISBLANK(D43), "", _xlfn.CONCAT("T", TEXT(B43, "0000"), "/", VLOOKUP(D43, Internal!$B$35:C$39, 2, FALSE), IF(OR(D43="QA", D43="Revision"), _xlfn.CONCAT("/", H43), "")))</f>
-        <v/>
-      </c>
-      <c r="D43" s="44"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
+        <v>T0033/QA/</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>40</v>
+      </c>
       <c r="H43" s="43"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
+      <c r="I43" s="46">
+        <v>46273.9375</v>
+      </c>
+      <c r="J43" s="46">
+        <v>46273.958333333336</v>
+      </c>
       <c r="K43" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Planned</v>
       </c>
       <c r="L43" s="47"/>
       <c r="M43" s="47"/>
@@ -7540,7 +8068,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -7571,7 +8099,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -7602,7 +8130,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -7633,7 +8161,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -7664,7 +8192,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -7695,7 +8223,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -7726,7 +8254,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -7757,7 +8285,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -7788,7 +8316,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -7819,7 +8347,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -7850,7 +8378,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -7881,7 +8409,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -7912,7 +8440,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -7943,7 +8471,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -7974,7 +8502,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -8005,7 +8533,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -8036,7 +8564,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -8067,7 +8595,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -8098,7 +8626,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -8129,7 +8657,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -8160,7 +8688,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -8191,7 +8719,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -8222,7 +8750,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -8253,7 +8781,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -8284,7 +8812,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -8315,7 +8843,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -8346,7 +8874,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -8377,7 +8905,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -8408,7 +8936,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -8439,7 +8967,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -8470,7 +8998,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -8501,7 +9029,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -8532,7 +9060,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -8563,7 +9091,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -8594,7 +9122,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -8625,7 +9153,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -8656,7 +9184,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -8687,7 +9215,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -8718,7 +9246,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -8749,7 +9277,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -8780,7 +9308,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -8811,7 +9339,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -8842,7 +9370,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -8873,7 +9401,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -8904,7 +9432,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -8935,7 +9463,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -8966,7 +9494,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -8997,7 +9525,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -9028,7 +9556,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -9059,7 +9587,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -9090,7 +9618,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -9121,7 +9649,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -9152,7 +9680,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -9183,7 +9711,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -9214,7 +9742,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -9245,7 +9773,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -9276,7 +9804,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -9307,7 +9835,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -9338,7 +9866,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -9369,7 +9897,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -9400,7 +9928,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -9431,7 +9959,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -9462,7 +9990,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -9493,7 +10021,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -9524,7 +10052,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -9555,7 +10083,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -9586,7 +10114,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -9704,49 +10232,49 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="55" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C2" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -9762,8 +10290,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -9785,8 +10313,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="53"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
@@ -9796,7 +10324,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -9804,22 +10332,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="54" t="s">
+      <c r="L9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="54"/>
+      <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -9866,7 +10394,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -9897,7 +10425,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -9928,7 +10456,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -9959,7 +10487,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -9990,7 +10518,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -10021,7 +10549,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -10052,7 +10580,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -10083,7 +10611,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -10114,7 +10642,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -10145,7 +10673,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -10176,7 +10704,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -10207,7 +10735,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -10238,7 +10766,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -10269,7 +10797,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -10300,7 +10828,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -10331,7 +10859,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -10362,7 +10890,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -10393,7 +10921,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -10424,7 +10952,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -10455,7 +10983,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -10486,7 +11014,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -10517,7 +11045,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -10548,7 +11076,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -10579,7 +11107,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -10610,7 +11138,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -10641,7 +11169,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -10672,7 +11200,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -10703,7 +11231,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -10734,7 +11262,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -10765,7 +11293,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -10796,7 +11324,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -10827,7 +11355,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -10858,7 +11386,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -10889,7 +11417,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -10920,7 +11448,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -10951,7 +11479,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -10982,7 +11510,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -11013,7 +11541,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -11044,7 +11572,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -11075,7 +11603,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -11106,7 +11634,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -11137,7 +11665,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -11168,7 +11696,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -11199,7 +11727,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -11230,7 +11758,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -11261,7 +11789,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -11292,7 +11820,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -11323,7 +11851,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -11354,7 +11882,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -11385,7 +11913,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -11416,7 +11944,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -11447,7 +11975,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -11478,7 +12006,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -11509,7 +12037,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -11540,7 +12068,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -11571,7 +12099,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -11602,7 +12130,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -11633,7 +12161,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -11664,7 +12192,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -11695,7 +12223,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -11726,7 +12254,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -11757,7 +12285,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -11788,7 +12316,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -11819,7 +12347,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -11850,7 +12378,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -11881,7 +12409,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -11912,7 +12440,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -11943,7 +12471,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -11974,7 +12502,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -12005,7 +12533,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -12036,7 +12564,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -12067,7 +12595,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -12098,7 +12626,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -12129,7 +12657,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -12160,7 +12688,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -12191,7 +12719,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -12222,7 +12750,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -12253,7 +12781,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -12284,7 +12812,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -12315,7 +12843,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -12346,7 +12874,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -12377,7 +12905,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -12408,7 +12936,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -12439,7 +12967,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -12470,7 +12998,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -12501,7 +13029,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -12532,7 +13060,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -12563,7 +13091,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -12594,7 +13122,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -12625,7 +13153,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -12656,7 +13184,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -12687,7 +13215,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -12718,7 +13246,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -12749,7 +13277,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -12780,7 +13308,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -12811,7 +13339,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -12842,7 +13370,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -12873,7 +13401,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -12904,7 +13432,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -12935,7 +13463,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -13053,60 +13581,60 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="56" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B4" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -13117,7 +13645,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="25" t="s">
         <v>112</v>
       </c>
@@ -13130,7 +13658,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
@@ -13143,7 +13671,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
@@ -13156,7 +13684,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>61</v>
       </c>
@@ -13169,7 +13697,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
@@ -13182,7 +13710,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
@@ -13195,7 +13723,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
@@ -13208,7 +13736,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -13219,7 +13747,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" s="26" t="s">
         <v>113</v>
       </c>
@@ -13232,7 +13760,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="15" t="s">
         <v>114</v>
       </c>
@@ -13245,7 +13773,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="15" t="s">
         <v>115</v>
       </c>
@@ -13258,7 +13786,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
         <v>116</v>
       </c>
@@ -13271,7 +13799,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -13282,7 +13810,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="26" t="s">
         <v>117</v>
       </c>
@@ -13295,7 +13823,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="17">
         <v>45658</v>
       </c>
@@ -13308,7 +13836,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
         <v>118</v>
       </c>
@@ -13321,7 +13849,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -13332,7 +13860,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="27" t="s">
         <v>119</v>
       </c>
@@ -13349,7 +13877,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="19" t="s">
         <v>56</v>
       </c>
@@ -13372,7 +13900,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="19" t="s">
         <v>32</v>
       </c>
@@ -13399,7 +13927,7 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="19" t="s">
         <v>126</v>
       </c>
@@ -13424,7 +13952,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="19" t="s">
         <v>38</v>
       </c>
@@ -13451,7 +13979,7 @@
       </c>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="19" t="s">
         <v>51</v>
       </c>
@@ -13478,7 +14006,7 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="21" t="s">
         <v>105</v>
       </c>
@@ -13507,7 +14035,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="22" t="s">
         <v>54</v>
       </c>
@@ -13524,7 +14052,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="24"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -13535,7 +14063,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34" s="33" t="s">
         <v>137</v>
       </c>
@@ -13550,7 +14078,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35" s="21" t="s">
         <v>30</v>
       </c>
@@ -13565,7 +14093,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36" s="21" t="s">
         <v>35</v>
       </c>
@@ -13580,7 +14108,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37" s="21" t="s">
         <v>49</v>
       </c>
@@ -13595,7 +14123,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38" s="21" t="s">
         <v>141</v>
       </c>
@@ -13610,7 +14138,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" s="32" t="s">
         <v>54</v>
       </c>

--- a/reports/Planning Report.xlsx
+++ b/reports/Planning Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZMis_cosas\UNI\DP2_2026\Workspace-26\Projects\Acme-Starters-B\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mario\Desktop\Dp2\Workspace-26\Projects\Acme-Starters-B\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D25F628-DEFE-49A4-9EE7-4C8B69EDEC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFA4BA1-1FA5-4D37-933C-B1F402CD5A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="153">
   <si>
     <t>Copyright</t>
   </si>
@@ -503,6 +503,21 @@
   </si>
   <si>
     <t>T0003/M</t>
+  </si>
+  <si>
+    <t>T0006/D</t>
+  </si>
+  <si>
+    <t>Test formally with end to end testing, making testing reports</t>
+  </si>
+  <si>
+    <t>Test informally and report with the group</t>
+  </si>
+  <si>
+    <t>Implement the features decided in the document</t>
+  </si>
+  <si>
+    <t>T0017/R/</t>
   </si>
 </sst>
 </file>
@@ -879,17 +894,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1529,26 +1544,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BB59C7-21D2-4063-B60E-B9743CBEBCDD}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="56" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="57"/>
@@ -1560,7 +1575,7 @@
       <c r="I4" s="57"/>
       <c r="J4" s="57"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="57"/>
       <c r="C5" s="57"/>
       <c r="D5" s="57"/>
@@ -1571,7 +1586,7 @@
       <c r="I5" s="57"/>
       <c r="J5" s="57"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="57"/>
       <c r="C6" s="57"/>
       <c r="D6" s="57"/>
@@ -1582,7 +1597,7 @@
       <c r="I6" s="57"/>
       <c r="J6" s="57"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="57"/>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
@@ -1593,7 +1608,7 @@
       <c r="I7" s="57"/>
       <c r="J7" s="57"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="57"/>
       <c r="C8" s="57"/>
       <c r="D8" s="57"/>
@@ -1604,7 +1619,7 @@
       <c r="I8" s="57"/>
       <c r="J8" s="57"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
@@ -1615,7 +1630,7 @@
       <c r="I9" s="57"/>
       <c r="J9" s="57"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="57"/>
       <c r="C10" s="57"/>
       <c r="D10" s="57"/>
@@ -1626,7 +1641,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
       <c r="D11" s="57"/>
@@ -1637,7 +1652,7 @@
       <c r="I11" s="57"/>
       <c r="J11" s="57"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
       <c r="D12" s="57"/>
@@ -1661,22 +1676,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1687,42 +1702,42 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="56" t="s">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1733,7 +1748,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
         <v>4</v>
@@ -1746,7 +1761,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="58" t="s">
         <v>5</v>
@@ -1759,7 +1774,7 @@
       <c r="I9" s="58"/>
       <c r="J9" s="58"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="48"/>
       <c r="C10" s="58" t="s">
         <v>6</v>
@@ -1772,7 +1787,7 @@
       <c r="I10" s="58"/>
       <c r="J10" s="58"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="49"/>
       <c r="C11" s="52" t="s">
         <v>7</v>
@@ -1785,7 +1800,7 @@
       <c r="I11" s="52"/>
       <c r="J11" s="52"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="58" t="s">
         <v>8</v>
@@ -1813,49 +1828,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.85546875" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="55" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1871,8 +1886,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1894,8 +1909,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="53"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
@@ -1905,7 +1920,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1913,22 +1928,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="54" t="s">
+      <c r="L9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="54"/>
+      <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -1975,7 +1990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -2024,7 +2039,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -2073,7 +2088,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -2120,7 +2135,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -2167,7 +2182,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -2216,7 +2231,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -2265,7 +2280,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -2314,7 +2329,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -2363,7 +2378,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -2457,7 +2472,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -2506,7 +2521,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -2555,7 +2570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -2604,7 +2619,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -2653,7 +2668,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -2702,7 +2717,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -2751,7 +2766,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -2798,7 +2813,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -2845,7 +2860,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -2892,7 +2907,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -2939,7 +2954,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -2990,7 +3005,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -3041,7 +3056,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -3092,7 +3107,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -3143,7 +3158,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -3194,7 +3209,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -3241,7 +3256,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -3288,7 +3303,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -3339,7 +3354,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -3390,7 +3405,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -3441,7 +3456,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -3492,7 +3507,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -3543,7 +3558,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -3590,7 +3605,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -3637,7 +3652,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -3688,7 +3703,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -3739,7 +3754,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -3790,7 +3805,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -3841,7 +3856,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -3892,7 +3907,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -3943,7 +3958,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -3994,7 +4009,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -4045,7 +4060,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -4096,7 +4111,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -4147,7 +4162,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -4194,7 +4209,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -4241,7 +4256,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -4292,7 +4307,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -4343,7 +4358,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -4394,7 +4409,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -4445,7 +4460,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -4496,7 +4511,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -4547,7 +4562,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -4598,7 +4613,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -4649,7 +4664,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -4700,7 +4715,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -4751,7 +4766,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -4798,7 +4813,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -4845,7 +4860,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -4876,7 +4891,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -4907,7 +4922,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -4938,7 +4953,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -4969,7 +4984,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -5000,7 +5015,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -5031,7 +5046,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -5062,7 +5077,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -5093,7 +5108,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -5124,7 +5139,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -5155,7 +5170,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -5186,7 +5201,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -5217,7 +5232,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -5248,7 +5263,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -5279,7 +5294,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -5310,7 +5325,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -5341,7 +5356,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -5372,7 +5387,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -5403,7 +5418,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -5434,7 +5449,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -5465,7 +5480,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -5496,7 +5511,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -5527,7 +5542,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -5558,7 +5573,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -5589,7 +5604,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -5620,7 +5635,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -5651,7 +5666,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -5682,7 +5697,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -5713,7 +5728,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -5744,7 +5759,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -5775,7 +5790,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -5806,7 +5821,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -5837,7 +5852,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -5868,7 +5883,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -5899,7 +5914,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -5930,7 +5945,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -5961,7 +5976,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -5992,7 +6007,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -6023,7 +6038,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -6054,7 +6069,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -6085,7 +6100,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -6116,7 +6131,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -6235,49 +6250,49 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.85546875" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="55" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6293,8 +6308,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -6302,7 +6317,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>340</v>
+        <v>705</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -6316,18 +6331,18 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="53"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>322.49999600000001</v>
+        <v>768.74999600000001</v>
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -6335,22 +6350,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="54" t="s">
+      <c r="L9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="54"/>
+      <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -6397,7 +6412,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -6446,7 +6461,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -6497,7 +6512,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -6544,7 +6559,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -6591,7 +6606,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -6640,7 +6655,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -6685,9 +6700,11 @@
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>25</v>
       </c>
-      <c r="P16" s="44"/>
-    </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P16" s="44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -6734,348 +6751,546 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41">
         <v>8</v>
       </c>
       <c r="C18" s="42" t="str">
         <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
-        <v/>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
+        <v>T0008/O</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H18" s="43"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
+      <c r="I18" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J18" s="46">
+        <v>46139.729166666664</v>
+      </c>
       <c r="K18" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L18" s="47">
+        <v>2</v>
+      </c>
+      <c r="M18" s="47">
+        <v>2</v>
+      </c>
+      <c r="N18" s="45">
         <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O18" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O18" s="45">
         <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41">
         <v>9</v>
       </c>
       <c r="C19" s="42" t="str">
         <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
-        <v/>
-      </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
+        <v>T0009/O</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H19" s="43"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="I19" s="46">
+        <v>46142.729166666664</v>
+      </c>
+      <c r="J19" s="46">
+        <v>46142.8125</v>
+      </c>
       <c r="K19" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L19" s="47">
+        <v>2</v>
+      </c>
+      <c r="M19" s="47">
+        <v>2</v>
+      </c>
+      <c r="N19" s="45">
         <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O19" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O19" s="45">
         <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41">
         <v>10</v>
       </c>
       <c r="C20" s="42" t="str">
         <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
-        <v/>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+        <v>T0010/QA/T0006/D</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J20" s="46">
+        <v>46142.729166666664</v>
+      </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L20" s="47">
+        <v>2</v>
+      </c>
+      <c r="M20" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N20" s="45">
         <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O20" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O20" s="45">
         <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P20" s="44"/>
-    </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37.5</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41">
         <v>11</v>
       </c>
       <c r="C21" s="42" t="str">
         <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
-        <v/>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
+        <v>T0011/QA/T0006/D</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I21" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J21" s="46">
+        <v>46142.729166666664</v>
+      </c>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L21" s="47">
+        <v>2</v>
+      </c>
+      <c r="M21" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O21" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O21" s="45">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P21" s="44"/>
-    </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37.5</v>
+      </c>
+      <c r="P21" s="44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41">
         <v>12</v>
       </c>
       <c r="C22" s="42" t="str">
         <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
-        <v/>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+        <v>T0012/QA/T0006/D</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J22" s="46">
+        <v>46142.729166666664</v>
+      </c>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L22" s="47">
+        <v>2</v>
+      </c>
+      <c r="M22" s="47">
+        <v>2</v>
+      </c>
+      <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O22" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O22" s="45">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P22" s="44"/>
-    </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="P22" s="44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41">
         <v>13</v>
       </c>
       <c r="C23" s="42" t="str">
         <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
-        <v/>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
+        <v>T0013/QA/T0006/D</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" s="46">
+        <v>46139.645833333336</v>
+      </c>
+      <c r="J23" s="46">
+        <v>46142.729166666664</v>
+      </c>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L23" s="47">
+        <v>2</v>
+      </c>
+      <c r="M23" s="47">
+        <v>1.75</v>
+      </c>
+      <c r="N23" s="45">
         <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O23" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O23" s="45">
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P23" s="44"/>
-    </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>43.75</v>
+      </c>
+      <c r="P23" s="44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="41">
         <v>14</v>
       </c>
       <c r="C24" s="42" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v/>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+        <v>T0014/O</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H24" s="43"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="46">
+        <v>46116.645833333336</v>
+      </c>
+      <c r="J24" s="46">
+        <v>46116.729166666664</v>
+      </c>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L24" s="47">
+        <v>2</v>
+      </c>
+      <c r="M24" s="47">
+        <v>2</v>
+      </c>
+      <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O24" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O24" s="45">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="41">
         <v>15</v>
       </c>
       <c r="C25" s="42" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
+        <v>T0015/O</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
+      <c r="I25" s="46">
+        <v>46119.729166666664</v>
+      </c>
+      <c r="J25" s="46">
+        <v>46119.8125</v>
+      </c>
       <c r="K25" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L25" s="47">
+        <v>2</v>
+      </c>
+      <c r="M25" s="47">
+        <v>2</v>
+      </c>
+      <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O25" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O25" s="45">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="41">
         <v>16</v>
       </c>
       <c r="C26" s="42" t="str">
         <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
-        <v/>
-      </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
+        <v>T0016/QA/T0006/D</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" s="46">
+        <v>46116.645833333336</v>
+      </c>
+      <c r="J26" s="46">
+        <v>46120.8125</v>
+      </c>
       <c r="K26" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L26" s="47">
+        <v>4</v>
+      </c>
+      <c r="M26" s="47">
+        <v>7</v>
+      </c>
+      <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O26" s="45" t="str">
+        <v>120</v>
+      </c>
+      <c r="O26" s="45">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P26" s="44"/>
-    </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+      <c r="P26" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="41">
         <v>17</v>
       </c>
       <c r="C27" s="42" t="str">
         <f>IF(ISBLANK(D27), "", _xlfn.CONCAT("T", TEXT(B27, "0000"), "/", VLOOKUP(D27, Internal!$B$35:C$39, 2, FALSE), IF(OR(D27="QA", D27="Revision"), _xlfn.CONCAT("/", H27), "")))</f>
-        <v/>
-      </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="44"/>
+        <v>T0017/R/</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>106</v>
+      </c>
       <c r="H27" s="43"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
+      <c r="I27" s="46">
+        <v>46116.645833333336</v>
+      </c>
+      <c r="J27" s="46">
+        <v>46120.8125</v>
+      </c>
       <c r="K27" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L27" s="47">
+        <v>1</v>
+      </c>
+      <c r="M27" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N27" s="45">
         <f>IF(ISBLANK(L27), "", L27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O27" s="45" t="str">
+        <v>30</v>
+      </c>
+      <c r="O27" s="45">
         <f>IF(ISBLANK(M27), "", M27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="41">
         <v>18</v>
       </c>
       <c r="C28" s="42" t="str">
         <f>IF(ISBLANK(D28), "", _xlfn.CONCAT("T", TEXT(B28, "0000"), "/", VLOOKUP(D28, Internal!$B$35:C$39, 2, FALSE), IF(OR(D28="QA", D28="Revision"), _xlfn.CONCAT("/", H28), "")))</f>
-        <v/>
-      </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
+        <v>T0018/M</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="I28" s="46">
+        <v>46116.645833333336</v>
+      </c>
+      <c r="J28" s="46">
+        <v>46120.8125</v>
+      </c>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L28" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="N28" s="45">
         <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O28" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O28" s="45">
         <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>22.5</v>
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -7106,7 +7321,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -7137,7 +7352,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -7168,7 +7383,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -7199,7 +7414,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -7230,7 +7445,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -7261,7 +7476,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -7292,7 +7507,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -7323,7 +7538,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -7354,7 +7569,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -7385,7 +7600,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -7416,7 +7631,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -7447,7 +7662,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -7478,7 +7693,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -7509,7 +7724,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -7540,7 +7755,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -7571,7 +7786,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -7602,7 +7817,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -7633,7 +7848,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -7664,7 +7879,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -7695,7 +7910,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -7726,7 +7941,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -7757,7 +7972,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -7788,7 +8003,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -7819,7 +8034,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -7850,7 +8065,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -7881,7 +8096,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -7912,7 +8127,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -7943,7 +8158,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -7974,7 +8189,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -8005,7 +8220,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -8036,7 +8251,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -8067,7 +8282,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -8098,7 +8313,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -8129,7 +8344,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -8160,7 +8375,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -8191,7 +8406,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -8222,7 +8437,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -8253,7 +8468,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -8284,7 +8499,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -8315,7 +8530,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -8346,7 +8561,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -8377,7 +8592,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -8408,7 +8623,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -8439,7 +8654,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -8470,7 +8685,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -8501,7 +8716,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -8532,7 +8747,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -8563,7 +8778,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -8594,7 +8809,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -8625,7 +8840,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -8656,7 +8871,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -8687,7 +8902,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -8718,7 +8933,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -8749,7 +8964,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -8780,7 +8995,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -8811,7 +9026,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -8842,7 +9057,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -8873,7 +9088,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -8904,7 +9119,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -8935,7 +9150,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -8966,7 +9181,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -8997,7 +9212,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -9028,7 +9243,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -9059,7 +9274,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -9090,7 +9305,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -9121,7 +9336,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -9152,7 +9367,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -9183,7 +9398,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -9214,7 +9429,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -9245,7 +9460,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -9276,7 +9491,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -9307,7 +9522,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -9338,7 +9553,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -9369,7 +9584,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -9400,7 +9615,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -9431,7 +9646,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -9462,7 +9677,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -9493,7 +9708,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -9524,7 +9739,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -9555,7 +9770,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -9586,7 +9801,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -9631,9 +9846,9 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J18:J110">
+  <conditionalFormatting sqref="J29:J110">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AND(I18&lt;&gt;"",J18&lt;&gt;"", I18&gt;J18)</formula>
+      <formula>AND(I29&lt;&gt;"",J29&lt;&gt;"", I29&gt;J29)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
@@ -9643,7 +9858,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ORDER" prompt="Order numbers are internal data.  Do not change them._x000a_" sqref="B11:B110" xr:uid="{0B09FB1F-529C-418F-A4D3-EEA1B2B7C0CD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ID" prompt="The IDs are updated automatically.  Don't modify them manually" sqref="C11:C110" xr:uid="{C4D1B9B9-7453-4A54-9715-5FAD733BC680}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O110" xr:uid="{AD2C10DC-BB9D-4FC5-98CB-4ECF92DF631C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="P11:P110 K11:K110" xr:uid="{E5549F6F-C1FD-4A7F-AE83-0FCE85CAE310}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="K11:K110 P11:P110" xr:uid="{E5549F6F-C1FD-4A7F-AE83-0FCE85CAE310}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M110" xr:uid="{EF49B9F1-3706-404A-831D-71B9EB2897F9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Provide a succint description of the task.  If not possible, the provide a link to a document where is is described." sqref="P10" xr:uid="{ACDBA3AE-39AA-4FE4-8D1D-2F815BD24EF4}"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="L11:L110" xr:uid="{9EA1ECC0-18E2-4835-A169-0090ED74A30F}">
@@ -9684,7 +9899,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J18:J110</xm:sqref>
+          <xm:sqref>J29:J110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Start moment" prompt="Indicate the moment when the assignee starts working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{175B319B-7D79-46C0-980E-ECB0D923AF19}">
           <x14:formula1>
@@ -9693,7 +9908,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J17 I11:I110</xm:sqref>
+          <xm:sqref>J11:J28 I11:I110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9704,49 +9919,49 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.85546875" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="55" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="56" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -9762,8 +9977,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -9785,8 +10000,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="53"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
@@ -9796,7 +10011,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -9804,22 +10019,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="54" t="s">
+      <c r="L9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54" t="s">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="54"/>
+      <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -9866,7 +10081,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -9897,7 +10112,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -9928,7 +10143,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -9959,7 +10174,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -9990,7 +10205,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -10021,7 +10236,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -10052,7 +10267,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -10083,7 +10298,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -10114,7 +10329,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -10145,7 +10360,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -10176,7 +10391,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -10207,7 +10422,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -10238,7 +10453,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -10269,7 +10484,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -10300,7 +10515,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -10331,7 +10546,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -10362,7 +10577,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -10393,7 +10608,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -10424,7 +10639,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -10455,7 +10670,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -10486,7 +10701,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -10517,7 +10732,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -10548,7 +10763,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -10579,7 +10794,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -10610,7 +10825,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -10641,7 +10856,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -10672,7 +10887,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -10703,7 +10918,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -10734,7 +10949,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -10765,7 +10980,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -10796,7 +11011,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -10827,7 +11042,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -10858,7 +11073,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -10889,7 +11104,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -10920,7 +11135,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -10951,7 +11166,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -10982,7 +11197,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -11013,7 +11228,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -11044,7 +11259,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -11075,7 +11290,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -11106,7 +11321,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -11137,7 +11352,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -11168,7 +11383,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -11199,7 +11414,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -11230,7 +11445,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -11261,7 +11476,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -11292,7 +11507,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -11323,7 +11538,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -11354,7 +11569,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -11385,7 +11600,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -11416,7 +11631,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -11447,7 +11662,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -11478,7 +11693,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -11509,7 +11724,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -11540,7 +11755,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -11571,7 +11786,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -11602,7 +11817,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -11633,7 +11848,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -11664,7 +11879,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -11695,7 +11910,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -11726,7 +11941,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -11757,7 +11972,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -11788,7 +12003,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -11819,7 +12034,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -11850,7 +12065,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -11881,7 +12096,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -11912,7 +12127,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -11943,7 +12158,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -11974,7 +12189,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -12005,7 +12220,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -12036,7 +12251,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -12067,7 +12282,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -12098,7 +12313,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -12129,7 +12344,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -12160,7 +12375,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -12191,7 +12406,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -12222,7 +12437,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -12253,7 +12468,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -12284,7 +12499,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -12315,7 +12530,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -12346,7 +12561,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -12377,7 +12592,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -12408,7 +12623,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -12439,7 +12654,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -12470,7 +12685,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -12501,7 +12716,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -12532,7 +12747,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -12563,7 +12778,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -12594,7 +12809,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -12625,7 +12840,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -12656,7 +12871,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -12687,7 +12902,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -12718,7 +12933,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -12749,7 +12964,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -12780,7 +12995,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -12811,7 +13026,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -12842,7 +13057,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -12873,7 +13088,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -12904,7 +13119,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -12935,7 +13150,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -13053,60 +13268,60 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="56" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -13117,7 +13332,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
         <v>112</v>
       </c>
@@ -13130,7 +13345,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
@@ -13143,7 +13358,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
@@ -13156,7 +13371,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>61</v>
       </c>
@@ -13169,7 +13384,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
@@ -13182,7 +13397,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
@@ -13195,7 +13410,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
@@ -13208,7 +13423,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -13219,7 +13434,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>113</v>
       </c>
@@ -13232,7 +13447,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>114</v>
       </c>
@@ -13245,7 +13460,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>115</v>
       </c>
@@ -13258,7 +13473,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
         <v>116</v>
       </c>
@@ -13271,7 +13486,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -13282,7 +13497,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
         <v>117</v>
       </c>
@@ -13295,7 +13510,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="17">
         <v>45658</v>
       </c>
@@ -13308,7 +13523,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="s">
         <v>118</v>
       </c>
@@ -13321,7 +13536,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -13332,7 +13547,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="27" t="s">
         <v>119</v>
       </c>
@@ -13349,7 +13564,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
         <v>56</v>
       </c>
@@ -13372,7 +13587,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
         <v>32</v>
       </c>
@@ -13399,7 +13614,7 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
         <v>126</v>
       </c>
@@ -13424,7 +13639,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>38</v>
       </c>
@@ -13451,7 +13666,7 @@
       </c>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
         <v>51</v>
       </c>
@@ -13478,7 +13693,7 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
         <v>105</v>
       </c>
@@ -13507,7 +13722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
         <v>54</v>
       </c>
@@ -13524,7 +13739,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="24"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -13535,7 +13750,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="33" t="s">
         <v>137</v>
       </c>
@@ -13550,7 +13765,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
         <v>30</v>
       </c>
@@ -13565,7 +13780,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
         <v>35</v>
       </c>
@@ -13580,7 +13795,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
         <v>49</v>
       </c>
@@ -13595,7 +13810,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="21" t="s">
         <v>141</v>
       </c>
@@ -13610,7 +13825,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="32" t="s">
         <v>54</v>
       </c>

--- a/reports/Planning Report.xlsx
+++ b/reports/Planning Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mario\Desktop\Dp2\Workspace-26\Projects\Acme-Starters-B\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eramo\Desktop\Tercero\DP2\Proyecto\Workspace-26\Workspace-26\Projects\Acme-Starters-B\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFA4BA1-1FA5-4D37-933C-B1F402CD5A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEC8CA6-E22F-47B7-A2FC-421B8DF14CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="170">
   <si>
     <t>Copyright</t>
   </si>
@@ -505,19 +505,70 @@
     <t>T0003/M</t>
   </si>
   <si>
-    <t>T0006/D</t>
-  </si>
-  <si>
-    <t>Test formally with end to end testing, making testing reports</t>
-  </si>
-  <si>
-    <t>Test informally and report with the group</t>
-  </si>
-  <si>
-    <t>Implement the features decided in the document</t>
-  </si>
-  <si>
-    <t>T0017/R/</t>
+    <t>Create project class requirements B2</t>
+  </si>
+  <si>
+    <t>Create AdBanners requirements B5</t>
+  </si>
+  <si>
+    <t>Display ad banners B12</t>
+  </si>
+  <si>
+    <t>Review B5 y B12</t>
+  </si>
+  <si>
+    <t>T0008/D</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Create member squad and Multiplicities &amp; Constraints B3 y B4</t>
+  </si>
+  <si>
+    <t>T0009/D</t>
+  </si>
+  <si>
+    <t>Populate sample data of Project, Member and WorksIn</t>
+  </si>
+  <si>
+    <t>Feature list project and their components of member's projects B6</t>
+  </si>
+  <si>
+    <t>Feature Dashoard B11</t>
+  </si>
+  <si>
+    <t>T0018/D</t>
+  </si>
+  <si>
+    <t>Fix views and repository dashboard</t>
+  </si>
+  <si>
+    <t>Feature list project and their components of managers's projects B10</t>
+  </si>
+  <si>
+    <t>Feature of views Any, Authenticated and CRUD manager B8, B9 y B10</t>
+  </si>
+  <si>
+    <t>T0022/D</t>
+  </si>
+  <si>
+    <t>Review B10</t>
+  </si>
+  <si>
+    <t>Review B8 y B9</t>
+  </si>
+  <si>
+    <t>And view members in Member and Manager</t>
+  </si>
+  <si>
+    <t>Fix dashboard</t>
+  </si>
+  <si>
+    <t>Add and delete memebers of a project</t>
+  </si>
+  <si>
+    <t>Views members in Any-Authenticated and fix in this views but in Member and Manager</t>
   </si>
 </sst>
 </file>
@@ -1544,12 +1595,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BB59C7-21D2-4063-B60E-B9743CBEBCDD}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1613,7 @@
       <c r="I2" s="53"/>
       <c r="J2" s="53"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="54" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1626,7 @@
       <c r="I4" s="57"/>
       <c r="J4" s="57"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="57"/>
       <c r="C5" s="57"/>
       <c r="D5" s="57"/>
@@ -1586,7 +1637,7 @@
       <c r="I5" s="57"/>
       <c r="J5" s="57"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="57"/>
       <c r="C6" s="57"/>
       <c r="D6" s="57"/>
@@ -1597,7 +1648,7 @@
       <c r="I6" s="57"/>
       <c r="J6" s="57"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="57"/>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
@@ -1608,7 +1659,7 @@
       <c r="I7" s="57"/>
       <c r="J7" s="57"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="57"/>
       <c r="C8" s="57"/>
       <c r="D8" s="57"/>
@@ -1619,7 +1670,7 @@
       <c r="I8" s="57"/>
       <c r="J8" s="57"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
@@ -1630,7 +1681,7 @@
       <c r="I9" s="57"/>
       <c r="J9" s="57"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="57"/>
       <c r="C10" s="57"/>
       <c r="D10" s="57"/>
@@ -1641,7 +1692,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
       <c r="D11" s="57"/>
@@ -1652,7 +1703,7 @@
       <c r="I11" s="57"/>
       <c r="J11" s="57"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
       <c r="D12" s="57"/>
@@ -1676,9 +1727,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="53" t="s">
         <v>2</v>
       </c>
@@ -1691,7 +1742,7 @@
       <c r="I2" s="53"/>
       <c r="J2" s="53"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1702,7 +1753,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="54" t="s">
         <v>3</v>
       </c>
@@ -1715,7 +1766,7 @@
       <c r="I4" s="54"/>
       <c r="J4" s="54"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
       <c r="D5" s="54"/>
@@ -1726,7 +1777,7 @@
       <c r="I5" s="54"/>
       <c r="J5" s="54"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="54"/>
       <c r="C6" s="54"/>
       <c r="D6" s="54"/>
@@ -1737,7 +1788,7 @@
       <c r="I6" s="54"/>
       <c r="J6" s="54"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1748,7 +1799,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
         <v>4</v>
@@ -1761,7 +1812,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="C9" s="58" t="s">
         <v>5</v>
@@ -1774,7 +1825,7 @@
       <c r="I9" s="58"/>
       <c r="J9" s="58"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="48"/>
       <c r="C10" s="58" t="s">
         <v>6</v>
@@ -1787,7 +1838,7 @@
       <c r="I10" s="58"/>
       <c r="J10" s="58"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="49"/>
       <c r="C11" s="52" t="s">
         <v>7</v>
@@ -1800,7 +1851,7 @@
       <c r="I11" s="52"/>
       <c r="J11" s="52"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
       <c r="C12" s="58" t="s">
         <v>8</v>
@@ -1828,13 +1879,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C2" s="53" t="s">
         <v>9</v>
       </c>
@@ -1852,7 +1903,7 @@
       <c r="O2" s="53"/>
       <c r="P2" s="53"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
@@ -1870,7 +1921,7 @@
       <c r="O4" s="54"/>
       <c r="P4" s="54"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1886,7 +1937,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
@@ -1909,7 +1960,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
@@ -1920,7 +1971,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1943,7 +1994,7 @@
       <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -1990,7 +2041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -2039,7 +2090,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -2088,7 +2139,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -2135,7 +2186,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -2182,7 +2233,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -2231,7 +2282,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -2280,7 +2331,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -2329,7 +2380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -2378,7 +2429,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -2425,7 +2476,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -2472,7 +2523,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -2521,7 +2572,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -2570,7 +2621,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -2619,7 +2670,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -2668,7 +2719,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -2717,7 +2768,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -2766,7 +2817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -2813,7 +2864,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -2860,7 +2911,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -2907,7 +2958,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -2954,7 +3005,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -3005,7 +3056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -3056,7 +3107,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -3107,7 +3158,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -3158,7 +3209,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -3209,7 +3260,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -3256,7 +3307,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -3303,7 +3354,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -3354,7 +3405,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -3405,7 +3456,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -3456,7 +3507,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -3507,7 +3558,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -3558,7 +3609,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -3605,7 +3656,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -3652,7 +3703,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -3703,7 +3754,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -3754,7 +3805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -3805,7 +3856,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -3856,7 +3907,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -3907,7 +3958,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -3958,7 +4009,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -4009,7 +4060,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -4060,7 +4111,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -4111,7 +4162,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -4162,7 +4213,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -4209,7 +4260,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -4256,7 +4307,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -4307,7 +4358,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -4358,7 +4409,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -4409,7 +4460,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -4460,7 +4511,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -4511,7 +4562,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -4562,7 +4613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -4613,7 +4664,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -4664,7 +4715,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -4715,7 +4766,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -4766,7 +4817,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -4813,7 +4864,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -4860,7 +4911,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -4891,7 +4942,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -4922,7 +4973,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -4953,7 +5004,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -4984,7 +5035,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -5015,7 +5066,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -5046,7 +5097,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -5077,7 +5128,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -5108,7 +5159,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -5139,7 +5190,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -5170,7 +5221,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -5201,7 +5252,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -5232,7 +5283,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -5263,7 +5314,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -5294,7 +5345,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -5325,7 +5376,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -5356,7 +5407,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -5387,7 +5438,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -5418,7 +5469,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -5449,7 +5500,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -5480,7 +5531,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -5511,7 +5562,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -5542,7 +5593,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -5573,7 +5624,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -5604,7 +5655,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -5635,7 +5686,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -5666,7 +5717,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -5697,7 +5748,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -5728,7 +5779,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -5759,7 +5810,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -5790,7 +5841,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -5821,7 +5872,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -5852,7 +5903,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -5883,7 +5934,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -5914,7 +5965,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -5945,7 +5996,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -5976,7 +6027,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -6007,7 +6058,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -6038,7 +6089,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -6069,7 +6120,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -6100,7 +6151,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -6131,7 +6182,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -6250,13 +6301,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C2" s="53" t="s">
         <v>108</v>
       </c>
@@ -6274,7 +6325,7 @@
       <c r="O2" s="53"/>
       <c r="P2" s="53"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
@@ -6292,7 +6343,7 @@
       <c r="O4" s="54"/>
       <c r="P4" s="54"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6308,7 +6359,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
@@ -6317,7 +6368,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>705</v>
+        <v>1563.75</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -6331,18 +6382,18 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>768.74999600000001</v>
+        <v>1689.999996</v>
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -6365,7 +6416,7 @@
       <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -6412,7 +6463,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -6461,7 +6512,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -6512,7 +6563,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -6559,7 +6610,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -6606,7 +6657,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -6655,7 +6706,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -6701,10 +6752,10 @@
         <v>25</v>
       </c>
       <c r="P16" s="44" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -6751,113 +6802,117 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="41">
         <v>8</v>
       </c>
       <c r="C18" s="42" t="str">
         <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
-        <v>T0008/O</v>
+        <v>T0008/D</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="46">
-        <v>46139.645833333336</v>
+        <v>46136.416666666664</v>
       </c>
       <c r="J18" s="46">
-        <v>46139.729166666664</v>
+        <v>46136.496527777781</v>
       </c>
       <c r="K18" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L18" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18" s="45">
         <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O18" s="45">
         <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="44"/>
-    </row>
-    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="41">
         <v>9</v>
       </c>
       <c r="C19" s="42" t="str">
         <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
-        <v>T0009/O</v>
+        <v>T0009/D</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H19" s="43"/>
       <c r="I19" s="46">
-        <v>46142.729166666664</v>
+        <v>46137.375</v>
       </c>
       <c r="J19" s="46">
-        <v>46142.8125</v>
+        <v>46137.75</v>
       </c>
       <c r="K19" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L19" s="47">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M19" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="45">
         <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="O19" s="45">
         <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="P19" s="44"/>
-    </row>
-    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="P19" s="44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="41">
         <v>10</v>
       </c>
       <c r="C20" s="42" t="str">
         <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
-        <v>T0010/QA/T0006/D</v>
+        <v>T0010/R/T0009/D</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F20" s="43" t="s">
         <v>38</v>
@@ -6866,115 +6921,113 @@
         <v>130</v>
       </c>
       <c r="H20" s="43" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I20" s="46">
-        <v>46139.645833333336</v>
+        <v>46138.5</v>
       </c>
       <c r="J20" s="46">
-        <v>46142.729166666664</v>
+        <v>46138.510416666664</v>
       </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L20" s="47">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M20" s="47">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="N20" s="45">
         <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="O20" s="45">
         <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>37.5</v>
+        <v>6.25</v>
       </c>
       <c r="P20" s="44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="41">
         <v>11</v>
       </c>
       <c r="C21" s="42" t="str">
         <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
-        <v>T0011/QA/T0006/D</v>
+        <v>T0011/D</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F21" s="43" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="H21" s="43" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I21" s="46">
-        <v>46139.645833333336</v>
+        <v>46138.520833333336</v>
       </c>
       <c r="J21" s="46">
-        <v>46142.729166666664</v>
+        <v>46138.583333333336</v>
       </c>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L21" s="47">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M21" s="47">
         <v>1.5</v>
       </c>
       <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="O21" s="45">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>37.5</v>
       </c>
       <c r="P21" s="44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="41">
         <v>12</v>
       </c>
       <c r="C22" s="42" t="str">
         <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
-        <v>T0012/QA/T0006/D</v>
+        <v>T0012/QA/</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>49</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="43" t="s">
-        <v>148</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H22" s="43"/>
       <c r="I22" s="46">
         <v>46139.645833333336</v>
       </c>
       <c r="J22" s="46">
-        <v>46142.729166666664</v>
+        <v>46139.722222222219</v>
       </c>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6988,44 +7041,42 @@
       </c>
       <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O22" s="45">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>50</v>
-      </c>
-      <c r="P22" s="44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="44"/>
+    </row>
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="41">
         <v>13</v>
       </c>
       <c r="C23" s="42" t="str">
         <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
-        <v>T0013/QA/T0006/D</v>
+        <v>T0013/QA/T0008/D</v>
       </c>
       <c r="D23" s="44" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I23" s="46">
         <v>46139.645833333336</v>
       </c>
       <c r="J23" s="46">
-        <v>46142.729166666664</v>
+        <v>46139.833333333336</v>
       </c>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7035,688 +7086,938 @@
         <v>2</v>
       </c>
       <c r="M23" s="47">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="N23" s="45">
         <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O23" s="45">
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>43.75</v>
+        <v>75</v>
       </c>
       <c r="P23" s="44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="41">
         <v>14</v>
       </c>
       <c r="C24" s="42" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v>T0014/O</v>
+        <v>T0014/D</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F24" s="43" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H24" s="43"/>
       <c r="I24" s="46">
-        <v>46116.645833333336</v>
+        <v>46140.375</v>
       </c>
       <c r="J24" s="46">
-        <v>46116.729166666664</v>
+        <v>46141.722222222219</v>
       </c>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L24" s="47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M24" s="47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="O24" s="45">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="44"/>
-    </row>
-    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="P24" s="44" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="41">
         <v>15</v>
       </c>
       <c r="C25" s="42" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v>T0015/O</v>
+        <v>T0015/R/T0014/D</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" s="43"/>
+        <v>130</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>69</v>
+      </c>
       <c r="I25" s="46">
-        <v>46119.729166666664</v>
+        <v>46141.520833333336</v>
       </c>
       <c r="J25" s="46">
-        <v>46119.8125</v>
+        <v>46141.53125</v>
       </c>
       <c r="K25" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L25" s="47">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M25" s="47">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O25" s="45">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="41">
         <v>16</v>
       </c>
       <c r="C26" s="42" t="str">
         <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
-        <v>T0016/QA/T0006/D</v>
+        <v>T0016/D</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F26" s="43" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="H26" s="43" t="s">
-        <v>148</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H26" s="43"/>
       <c r="I26" s="46">
-        <v>46116.645833333336</v>
+        <v>46142.416666666664</v>
       </c>
       <c r="J26" s="46">
-        <v>46120.8125</v>
+        <v>46143.833333333336</v>
       </c>
       <c r="K26" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L26" s="47">
+        <v>3</v>
+      </c>
+      <c r="M26" s="47">
         <v>4</v>
-      </c>
-      <c r="M26" s="47">
-        <v>7</v>
       </c>
       <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="O26" s="45">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="P26" s="44" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="41">
         <v>17</v>
       </c>
       <c r="C27" s="42" t="str">
         <f>IF(ISBLANK(D27), "", _xlfn.CONCAT("T", TEXT(B27, "0000"), "/", VLOOKUP(D27, Internal!$B$35:C$39, 2, FALSE), IF(OR(D27="QA", D27="Revision"), _xlfn.CONCAT("/", H27), "")))</f>
-        <v>T0017/R/</v>
+        <v>T0017/QA/</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="H27" s="43"/>
       <c r="I27" s="46">
-        <v>46116.645833333336</v>
+        <v>46142.736111111109</v>
       </c>
       <c r="J27" s="46">
-        <v>46120.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="K27" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L27" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="47">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N27" s="45">
         <f>IF(ISBLANK(L27), "", L27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O27" s="45">
         <f>IF(ISBLANK(M27), "", M27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="41">
         <v>18</v>
       </c>
       <c r="C28" s="42" t="str">
         <f>IF(ISBLANK(D28), "", _xlfn.CONCAT("T", TEXT(B28, "0000"), "/", VLOOKUP(D28, Internal!$B$35:C$39, 2, FALSE), IF(OR(D28="QA", D28="Revision"), _xlfn.CONCAT("/", H28), "")))</f>
-        <v>T0018/M</v>
+        <v>T0018/D</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="H28" s="43" t="s">
-        <v>152</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H28" s="43"/>
       <c r="I28" s="46">
-        <v>46116.645833333336</v>
+        <v>46142.833333333336</v>
       </c>
       <c r="J28" s="46">
-        <v>46120.8125</v>
+        <v>46143.5</v>
       </c>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Completed</v>
       </c>
       <c r="L28" s="47">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="M28" s="47">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="N28" s="45">
         <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="O28" s="45">
         <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>22.5</v>
-      </c>
-      <c r="P28" s="44"/>
-    </row>
-    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="P28" s="44" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="41">
         <v>19</v>
       </c>
       <c r="C29" s="42" t="str">
         <f>IF(ISBLANK(D29), "", _xlfn.CONCAT("T", TEXT(B29, "0000"), "/", VLOOKUP(D29, Internal!$B$35:C$39, 2, FALSE), IF(OR(D29="QA", D29="Revision"), _xlfn.CONCAT("/", H29), "")))</f>
-        <v/>
-      </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
+        <v>T0019/D</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="46">
+        <v>46144.375</v>
+      </c>
+      <c r="J29" s="46">
+        <v>46144.385416666664</v>
+      </c>
       <c r="K29" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L29" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N29" s="45">
         <f>IF(ISBLANK(L29), "", L29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O29" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O29" s="45">
         <f>IF(ISBLANK(M29), "", M29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>6.25</v>
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="41">
         <v>20</v>
       </c>
       <c r="C30" s="42" t="str">
         <f>IF(ISBLANK(D30), "", _xlfn.CONCAT("T", TEXT(B30, "0000"), "/", VLOOKUP(D30, Internal!$B$35:C$39, 2, FALSE), IF(OR(D30="QA", D30="Revision"), _xlfn.CONCAT("/", H30), "")))</f>
-        <v/>
-      </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+        <v>T0020/D</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="I30" s="46">
+        <v>46144.5</v>
+      </c>
+      <c r="J30" s="46">
+        <v>46144.510416666664</v>
+      </c>
       <c r="K30" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L30" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M30" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N30" s="45">
         <f>IF(ISBLANK(L30), "", L30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O30" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O30" s="45">
         <f>IF(ISBLANK(M30), "", M30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>6.25</v>
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="41">
         <v>21</v>
       </c>
       <c r="C31" s="42" t="str">
         <f>IF(ISBLANK(D31), "", _xlfn.CONCAT("T", TEXT(B31, "0000"), "/", VLOOKUP(D31, Internal!$B$35:C$39, 2, FALSE), IF(OR(D31="QA", D31="Revision"), _xlfn.CONCAT("/", H31), "")))</f>
-        <v/>
-      </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
+        <v>T0021/D</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="46">
+        <v>46147.375</v>
+      </c>
+      <c r="J31" s="46">
+        <v>46147.5</v>
+      </c>
       <c r="K31" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L31" s="47">
+        <v>1</v>
+      </c>
+      <c r="M31" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N31" s="45">
         <f>IF(ISBLANK(L31), "", L31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O31" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O31" s="45">
         <f>IF(ISBLANK(M31), "", M31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P31" s="44"/>
-    </row>
-    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>37.5</v>
+      </c>
+      <c r="P31" s="44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="41">
         <v>22</v>
       </c>
       <c r="C32" s="42" t="str">
         <f>IF(ISBLANK(D32), "", _xlfn.CONCAT("T", TEXT(B32, "0000"), "/", VLOOKUP(D32, Internal!$B$35:C$39, 2, FALSE), IF(OR(D32="QA", D32="Revision"), _xlfn.CONCAT("/", H32), "")))</f>
-        <v/>
-      </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
+        <v>T0022/D</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H32" s="43"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
+      <c r="I32" s="46">
+        <v>46145.416666666664</v>
+      </c>
+      <c r="J32" s="46">
+        <v>46146.958333333336</v>
+      </c>
       <c r="K32" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L32" s="47">
+        <v>5</v>
+      </c>
+      <c r="M32" s="47">
+        <v>7</v>
+      </c>
+      <c r="N32" s="45">
         <f>IF(ISBLANK(L32), "", L32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O32" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O32" s="45">
         <f>IF(ISBLANK(M32), "", M32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P32" s="44"/>
-    </row>
-    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+      <c r="P32" s="44" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="41">
         <v>23</v>
       </c>
       <c r="C33" s="42" t="str">
         <f>IF(ISBLANK(D33), "", _xlfn.CONCAT("T", TEXT(B33, "0000"), "/", VLOOKUP(D33, Internal!$B$35:C$39, 2, FALSE), IF(OR(D33="QA", D33="Revision"), _xlfn.CONCAT("/", H33), "")))</f>
-        <v/>
-      </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+        <v>T0023/QA/</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H33" s="43"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
+      <c r="I33" s="46">
+        <v>46146.645833333336</v>
+      </c>
+      <c r="J33" s="46">
+        <v>46146.729166666664</v>
+      </c>
       <c r="K33" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L33" s="47">
+        <v>2</v>
+      </c>
+      <c r="M33" s="47">
+        <v>2</v>
+      </c>
+      <c r="N33" s="45">
         <f>IF(ISBLANK(L33), "", L33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O33" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O33" s="45">
         <f>IF(ISBLANK(M33), "", M33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="41">
         <v>24</v>
       </c>
       <c r="C34" s="42" t="str">
         <f>IF(ISBLANK(D34), "", _xlfn.CONCAT("T", TEXT(B34, "0000"), "/", VLOOKUP(D34, Internal!$B$35:C$39, 2, FALSE), IF(OR(D34="QA", D34="Revision"), _xlfn.CONCAT("/", H34), "")))</f>
-        <v/>
-      </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
+        <v>T0024/R/T0022/D</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="I34" s="46">
+        <v>46147.375</v>
+      </c>
+      <c r="J34" s="46">
+        <v>46147.458333333336</v>
+      </c>
       <c r="K34" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L34" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N34" s="45">
         <f>IF(ISBLANK(L34), "", L34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O34" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O34" s="45">
         <f>IF(ISBLANK(M34), "", M34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P34" s="44"/>
-    </row>
-    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>37.5</v>
+      </c>
+      <c r="P34" s="44" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="41">
         <v>25</v>
       </c>
       <c r="C35" s="42" t="str">
         <f>IF(ISBLANK(D35), "", _xlfn.CONCAT("T", TEXT(B35, "0000"), "/", VLOOKUP(D35, Internal!$B$35:C$39, 2, FALSE), IF(OR(D35="QA", D35="Revision"), _xlfn.CONCAT("/", H35), "")))</f>
-        <v/>
-      </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
+        <v>T0025/R/T0022/D</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="I35" s="46">
+        <v>46147.416666666664</v>
+      </c>
+      <c r="J35" s="46">
+        <v>46147.458333333336</v>
+      </c>
       <c r="K35" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L35" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="47">
+        <v>1</v>
+      </c>
+      <c r="N35" s="45">
         <f>IF(ISBLANK(L35), "", L35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O35" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O35" s="45">
         <f>IF(ISBLANK(M35), "", M35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P35" s="44"/>
-    </row>
-    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="P35" s="44" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="41">
         <v>26</v>
       </c>
       <c r="C36" s="42" t="str">
         <f>IF(ISBLANK(D36), "", _xlfn.CONCAT("T", TEXT(B36, "0000"), "/", VLOOKUP(D36, Internal!$B$35:C$39, 2, FALSE), IF(OR(D36="QA", D36="Revision"), _xlfn.CONCAT("/", H36), "")))</f>
-        <v/>
-      </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+        <v>T0026/D</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
+      <c r="I36" s="46">
+        <v>46148.520833333336</v>
+      </c>
+      <c r="J36" s="46">
+        <v>46148.822916666664</v>
+      </c>
       <c r="K36" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L36" s="47">
+        <v>2</v>
+      </c>
+      <c r="M36" s="47">
+        <v>2.25</v>
+      </c>
+      <c r="N36" s="45">
         <f>IF(ISBLANK(L36), "", L36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O36" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O36" s="45">
         <f>IF(ISBLANK(M36), "", M36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P36" s="44"/>
-    </row>
-    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>56.25</v>
+      </c>
+      <c r="P36" s="44" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="41">
         <v>27</v>
       </c>
       <c r="C37" s="42" t="str">
         <f>IF(ISBLANK(D37), "", _xlfn.CONCAT("T", TEXT(B37, "0000"), "/", VLOOKUP(D37, Internal!$B$35:C$39, 2, FALSE), IF(OR(D37="QA", D37="Revision"), _xlfn.CONCAT("/", H37), "")))</f>
-        <v/>
-      </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
+        <v>T0027/D</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H37" s="43"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
+      <c r="I37" s="46">
+        <v>46148.541666666664</v>
+      </c>
+      <c r="J37" s="46">
+        <v>46148.645833333336</v>
+      </c>
       <c r="K37" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L37" s="47"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L37" s="47">
+        <v>1</v>
+      </c>
+      <c r="M37" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="N37" s="45">
         <f>IF(ISBLANK(L37), "", L37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O37" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O37" s="45">
         <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P37" s="44"/>
-    </row>
-    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>18.75</v>
+      </c>
+      <c r="P37" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="41">
         <v>28</v>
       </c>
       <c r="C38" s="42" t="str">
         <f>IF(ISBLANK(D38), "", _xlfn.CONCAT("T", TEXT(B38, "0000"), "/", VLOOKUP(D38, Internal!$B$35:C$39, 2, FALSE), IF(OR(D38="QA", D38="Revision"), _xlfn.CONCAT("/", H38), "")))</f>
-        <v/>
-      </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+        <v>T0028/D</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H38" s="43"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
+      <c r="I38" s="46">
+        <v>46148.645833333336</v>
+      </c>
+      <c r="J38" s="46">
+        <v>46150.166666666664</v>
+      </c>
       <c r="K38" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L38" s="47">
+        <v>5</v>
+      </c>
+      <c r="M38" s="47">
+        <v>8</v>
+      </c>
+      <c r="N38" s="45">
         <f>IF(ISBLANK(L38), "", L38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O38" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O38" s="45">
         <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P38" s="44"/>
-    </row>
-    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+      <c r="P38" s="44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="41">
         <v>29</v>
       </c>
       <c r="C39" s="42" t="str">
         <f>IF(ISBLANK(D39), "", _xlfn.CONCAT("T", TEXT(B39, "0000"), "/", VLOOKUP(D39, Internal!$B$35:C$39, 2, FALSE), IF(OR(D39="QA", D39="Revision"), _xlfn.CONCAT("/", H39), "")))</f>
-        <v/>
-      </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
+        <v>T0029/D</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H39" s="43"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
+      <c r="I39" s="46">
+        <v>46149.5</v>
+      </c>
+      <c r="J39" s="46">
+        <v>46149.958333333336</v>
+      </c>
       <c r="K39" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L39" s="47">
+        <v>3</v>
+      </c>
+      <c r="M39" s="47">
+        <v>4</v>
+      </c>
+      <c r="N39" s="45">
         <f>IF(ISBLANK(L39), "", L39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O39" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O39" s="45">
         <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P39" s="44"/>
-    </row>
-    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="P39" s="44" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="41">
         <v>30</v>
       </c>
       <c r="C40" s="42" t="str">
         <f>IF(ISBLANK(D40), "", _xlfn.CONCAT("T", TEXT(B40, "0000"), "/", VLOOKUP(D40, Internal!$B$35:C$39, 2, FALSE), IF(OR(D40="QA", D40="Revision"), _xlfn.CONCAT("/", H40), "")))</f>
-        <v/>
-      </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="44"/>
+        <v>T0030/QA/</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="H40" s="43"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
+      <c r="I40" s="46">
+        <v>46149.736111111109</v>
+      </c>
+      <c r="J40" s="46">
+        <v>46149.8125</v>
+      </c>
       <c r="K40" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L40" s="47"/>
-      <c r="M40" s="47"/>
-      <c r="N40" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L40" s="47">
+        <v>2</v>
+      </c>
+      <c r="M40" s="47">
+        <v>2</v>
+      </c>
+      <c r="N40" s="45">
         <f>IF(ISBLANK(L40), "", L40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O40" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O40" s="45">
         <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="41">
         <v>31</v>
       </c>
       <c r="C41" s="42" t="str">
         <f>IF(ISBLANK(D41), "", _xlfn.CONCAT("T", TEXT(B41, "0000"), "/", VLOOKUP(D41, Internal!$B$35:C$39, 2, FALSE), IF(OR(D41="QA", D41="Revision"), _xlfn.CONCAT("/", H41), "")))</f>
-        <v/>
-      </c>
-      <c r="D41" s="44"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
+        <v>T0031/R/</v>
+      </c>
+      <c r="D41" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>132</v>
+      </c>
       <c r="H41" s="43"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
+      <c r="I41" s="46">
+        <v>46150.375</v>
+      </c>
+      <c r="J41" s="46">
+        <v>46150.9375</v>
+      </c>
       <c r="K41" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L41" s="47"/>
-      <c r="M41" s="47"/>
-      <c r="N41" s="45" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="L41" s="47">
+        <v>5</v>
+      </c>
+      <c r="M41" s="47">
+        <v>6</v>
+      </c>
+      <c r="N41" s="45">
         <f>IF(ISBLANK(L41), "", L41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O41" s="45" t="str">
+        <v>150</v>
+      </c>
+      <c r="O41" s="45">
         <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="41">
         <v>32</v>
       </c>
       <c r="C42" s="42" t="str">
         <f>IF(ISBLANK(D42), "", _xlfn.CONCAT("T", TEXT(B42, "0000"), "/", VLOOKUP(D42, Internal!$B$35:C$39, 2, FALSE), IF(OR(D42="QA", D42="Revision"), _xlfn.CONCAT("/", H42), "")))</f>
-        <v/>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="44"/>
+        <v>T0032/R/</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>133</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
+      <c r="I42" s="46">
+        <v>46273.5</v>
+      </c>
+      <c r="J42" s="46">
+        <v>46273.9375</v>
+      </c>
       <c r="K42" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L42" s="47"/>
+        <v>Planned</v>
+      </c>
+      <c r="L42" s="47">
+        <v>4</v>
+      </c>
       <c r="M42" s="47"/>
-      <c r="N42" s="45" t="str">
+      <c r="N42" s="45">
         <f>IF(ISBLANK(L42), "", L42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="O42" s="45" t="str">
         <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
@@ -7724,24 +8025,36 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="41">
         <v>33</v>
       </c>
       <c r="C43" s="42" t="str">
         <f>IF(ISBLANK(D43), "", _xlfn.CONCAT("T", TEXT(B43, "0000"), "/", VLOOKUP(D43, Internal!$B$35:C$39, 2, FALSE), IF(OR(D43="QA", D43="Revision"), _xlfn.CONCAT("/", H43), "")))</f>
-        <v/>
-      </c>
-      <c r="D43" s="44"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
+        <v>T0033/QA/</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>40</v>
+      </c>
       <c r="H43" s="43"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
+      <c r="I43" s="46">
+        <v>46273.9375</v>
+      </c>
+      <c r="J43" s="46">
+        <v>46273.958333333336</v>
+      </c>
       <c r="K43" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Planned</v>
       </c>
       <c r="L43" s="47"/>
       <c r="M43" s="47"/>
@@ -7755,7 +8068,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -7786,7 +8099,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -7817,7 +8130,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -7848,7 +8161,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -7879,7 +8192,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -7910,7 +8223,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -7941,7 +8254,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -7972,7 +8285,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -8003,7 +8316,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -8034,7 +8347,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -8065,7 +8378,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -8096,7 +8409,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -8127,7 +8440,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -8158,7 +8471,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -8189,7 +8502,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -8220,7 +8533,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -8251,7 +8564,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -8282,7 +8595,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -8313,7 +8626,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -8344,7 +8657,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -8375,7 +8688,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -8406,7 +8719,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -8437,7 +8750,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -8468,7 +8781,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -8499,7 +8812,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -8530,7 +8843,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -8561,7 +8874,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -8592,7 +8905,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -8623,7 +8936,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -8654,7 +8967,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -8685,7 +8998,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -8716,7 +9029,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -8747,7 +9060,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -8778,7 +9091,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -8809,7 +9122,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -8840,7 +9153,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -8871,7 +9184,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -8902,7 +9215,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -8933,7 +9246,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -8964,7 +9277,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -8995,7 +9308,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -9026,7 +9339,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -9057,7 +9370,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -9088,7 +9401,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -9119,7 +9432,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -9150,7 +9463,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -9181,7 +9494,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -9212,7 +9525,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -9243,7 +9556,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -9274,7 +9587,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -9305,7 +9618,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -9336,7 +9649,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -9367,7 +9680,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -9398,7 +9711,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -9429,7 +9742,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -9460,7 +9773,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -9491,7 +9804,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -9522,7 +9835,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -9553,7 +9866,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -9584,7 +9897,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -9615,7 +9928,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -9646,7 +9959,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -9677,7 +9990,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -9708,7 +10021,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -9739,7 +10052,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -9770,7 +10083,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -9801,7 +10114,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -9846,9 +10159,9 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29:J110">
+  <conditionalFormatting sqref="J18:J110">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AND(I29&lt;&gt;"",J29&lt;&gt;"", I29&gt;J29)</formula>
+      <formula>AND(I18&lt;&gt;"",J18&lt;&gt;"", I18&gt;J18)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
@@ -9858,7 +10171,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ORDER" prompt="Order numbers are internal data.  Do not change them._x000a_" sqref="B11:B110" xr:uid="{0B09FB1F-529C-418F-A4D3-EEA1B2B7C0CD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ID" prompt="The IDs are updated automatically.  Don't modify them manually" sqref="C11:C110" xr:uid="{C4D1B9B9-7453-4A54-9715-5FAD733BC680}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O110" xr:uid="{AD2C10DC-BB9D-4FC5-98CB-4ECF92DF631C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="K11:K110 P11:P110" xr:uid="{E5549F6F-C1FD-4A7F-AE83-0FCE85CAE310}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="P11:P110 K11:K110" xr:uid="{E5549F6F-C1FD-4A7F-AE83-0FCE85CAE310}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M110" xr:uid="{EF49B9F1-3706-404A-831D-71B9EB2897F9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Provide a succint description of the task.  If not possible, the provide a link to a document where is is described." sqref="P10" xr:uid="{ACDBA3AE-39AA-4FE4-8D1D-2F815BD24EF4}"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="L11:L110" xr:uid="{9EA1ECC0-18E2-4835-A169-0090ED74A30F}">
@@ -9899,7 +10212,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J29:J110</xm:sqref>
+          <xm:sqref>J18:J110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Start moment" prompt="Indicate the moment when the assignee starts working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{175B319B-7D79-46C0-980E-ECB0D923AF19}">
           <x14:formula1>
@@ -9908,7 +10221,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J28 I11:I110</xm:sqref>
+          <xm:sqref>J11:J17 I11:I110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9919,13 +10232,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C2" s="53" t="s">
         <v>109</v>
       </c>
@@ -9943,7 +10256,7 @@
       <c r="O2" s="53"/>
       <c r="P2" s="53"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="54" t="s">
         <v>10</v>
       </c>
@@ -9961,7 +10274,7 @@
       <c r="O4" s="54"/>
       <c r="P4" s="54"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -9977,7 +10290,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C6" s="55" t="s">
         <v>11</v>
       </c>
@@ -10000,7 +10313,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C7" s="55"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
@@ -10011,7 +10324,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -10034,7 +10347,7 @@
       <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -10081,7 +10394,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -10112,7 +10425,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -10143,7 +10456,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -10174,7 +10487,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -10205,7 +10518,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -10236,7 +10549,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -10267,7 +10580,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -10298,7 +10611,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -10329,7 +10642,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -10360,7 +10673,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -10391,7 +10704,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -10422,7 +10735,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -10453,7 +10766,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -10484,7 +10797,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -10515,7 +10828,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -10546,7 +10859,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -10577,7 +10890,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -10608,7 +10921,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -10639,7 +10952,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -10670,7 +10983,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -10701,7 +11014,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -10732,7 +11045,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -10763,7 +11076,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -10794,7 +11107,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -10825,7 +11138,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -10856,7 +11169,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -10887,7 +11200,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -10918,7 +11231,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -10949,7 +11262,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -10980,7 +11293,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -11011,7 +11324,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -11042,7 +11355,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -11073,7 +11386,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -11104,7 +11417,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -11135,7 +11448,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -11166,7 +11479,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -11197,7 +11510,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -11228,7 +11541,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -11259,7 +11572,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -11290,7 +11603,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -11321,7 +11634,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -11352,7 +11665,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -11383,7 +11696,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -11414,7 +11727,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -11445,7 +11758,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -11476,7 +11789,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -11507,7 +11820,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -11538,7 +11851,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -11569,7 +11882,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -11600,7 +11913,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -11631,7 +11944,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -11662,7 +11975,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -11693,7 +12006,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -11724,7 +12037,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -11755,7 +12068,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -11786,7 +12099,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -11817,7 +12130,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -11848,7 +12161,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -11879,7 +12192,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -11910,7 +12223,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -11941,7 +12254,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -11972,7 +12285,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -12003,7 +12316,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -12034,7 +12347,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -12065,7 +12378,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -12096,7 +12409,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -12127,7 +12440,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -12158,7 +12471,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -12189,7 +12502,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -12220,7 +12533,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -12251,7 +12564,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -12282,7 +12595,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -12313,7 +12626,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -12344,7 +12657,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -12375,7 +12688,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -12406,7 +12719,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -12437,7 +12750,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -12468,7 +12781,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -12499,7 +12812,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -12530,7 +12843,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -12561,7 +12874,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -12592,7 +12905,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -12623,7 +12936,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -12654,7 +12967,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -12685,7 +12998,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -12716,7 +13029,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -12747,7 +13060,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -12778,7 +13091,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -12809,7 +13122,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -12840,7 +13153,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -12871,7 +13184,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -12902,7 +13215,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -12933,7 +13246,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -12964,7 +13277,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -12995,7 +13308,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -13026,7 +13339,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -13057,7 +13370,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -13088,7 +13401,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -13119,7 +13432,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -13150,7 +13463,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -13268,12 +13581,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="53" t="s">
         <v>110</v>
       </c>
@@ -13286,7 +13599,7 @@
       <c r="I2" s="53"/>
       <c r="J2" s="53"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="54" t="s">
         <v>111</v>
       </c>
@@ -13299,7 +13612,7 @@
       <c r="I4" s="54"/>
       <c r="J4" s="54"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
       <c r="D5" s="54"/>
@@ -13310,7 +13623,7 @@
       <c r="I5" s="54"/>
       <c r="J5" s="54"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="54"/>
       <c r="C6" s="54"/>
       <c r="D6" s="54"/>
@@ -13321,7 +13634,7 @@
       <c r="I6" s="54"/>
       <c r="J6" s="54"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -13332,7 +13645,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="25" t="s">
         <v>112</v>
       </c>
@@ -13345,7 +13658,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
@@ -13358,7 +13671,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
@@ -13371,7 +13684,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>61</v>
       </c>
@@ -13384,7 +13697,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
@@ -13397,7 +13710,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
@@ -13410,7 +13723,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" s="14" t="s">
         <v>55</v>
       </c>
@@ -13423,7 +13736,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" s="3"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -13434,7 +13747,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" s="26" t="s">
         <v>113</v>
       </c>
@@ -13447,7 +13760,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="15" t="s">
         <v>114</v>
       </c>
@@ -13460,7 +13773,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="15" t="s">
         <v>115</v>
       </c>
@@ -13473,7 +13786,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
         <v>116</v>
       </c>
@@ -13486,7 +13799,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -13497,7 +13810,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="26" t="s">
         <v>117</v>
       </c>
@@ -13510,7 +13823,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="17">
         <v>45658</v>
       </c>
@@ -13523,7 +13836,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="18" t="s">
         <v>118</v>
       </c>
@@ -13536,7 +13849,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -13547,7 +13860,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="27" t="s">
         <v>119</v>
       </c>
@@ -13564,7 +13877,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="19" t="s">
         <v>56</v>
       </c>
@@ -13587,7 +13900,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="19" t="s">
         <v>32</v>
       </c>
@@ -13614,7 +13927,7 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="19" t="s">
         <v>126</v>
       </c>
@@ -13639,7 +13952,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="19" t="s">
         <v>38</v>
       </c>
@@ -13666,7 +13979,7 @@
       </c>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="19" t="s">
         <v>51</v>
       </c>
@@ -13693,7 +14006,7 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="21" t="s">
         <v>105</v>
       </c>
@@ -13722,7 +14035,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="22" t="s">
         <v>54</v>
       </c>
@@ -13739,7 +14052,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="24"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -13750,7 +14063,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34" s="33" t="s">
         <v>137</v>
       </c>
@@ -13765,7 +14078,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35" s="21" t="s">
         <v>30</v>
       </c>
@@ -13780,7 +14093,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36" s="21" t="s">
         <v>35</v>
       </c>
@@ -13795,7 +14108,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37" s="21" t="s">
         <v>49</v>
       </c>
@@ -13810,7 +14123,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38" s="21" t="s">
         <v>141</v>
       </c>
@@ -13825,7 +14138,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" s="32" t="s">
         <v>54</v>
       </c>
